--- a/research/traditional_assets/database/data/chile/chile_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_furn_home_furnishings.xlsx
@@ -1139,7 +1139,7 @@
         <v>6.47554806070826</v>
       </c>
       <c r="H2">
-        <v>4.4256323777403</v>
+        <v>4.42563237774031</v>
       </c>
       <c r="I2">
         <v>0.526748971193416</v>
@@ -1169,7 +1169,7 @@
         <v>0.090888074905956</v>
       </c>
       <c r="R2">
-        <v>0.0899066959451842</v>
+        <v>0.08990669594518411</v>
       </c>
       <c r="S2">
         <v>0.0483122072898587</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0968211076043245</v>
+        <v>0.09659254061379283</v>
       </c>
       <c r="C2">
-        <v>64.52893075215694</v>
+        <v>64.08620313912911</v>
       </c>
       <c r="D2">
-        <v>63.61593075215694</v>
+        <v>63.90220313912911</v>
       </c>
       <c r="E2">
-        <v>-38.4</v>
+        <v>-37.671</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7290000000000001</v>
       </c>
       <c r="G2">
         <v>0.913</v>
@@ -1451,28 +1451,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03666870000000001</v>
       </c>
       <c r="N2">
-        <v>6.643333333333333</v>
+        <v>6.606664633333333</v>
       </c>
       <c r="O2">
-        <v>1.7937</v>
+        <v>1.783799451</v>
       </c>
       <c r="P2">
-        <v>4.849633333333333</v>
+        <v>4.822865182333333</v>
       </c>
       <c r="Q2">
-        <v>8.089633333333333</v>
+        <v>8.062865182333333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0968211076043245</v>
+        <v>0.09719732385231598</v>
       </c>
       <c r="T2">
-        <v>0.9344695036460947</v>
+        <v>0.9413600363497479</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>181.1717713835869</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09659254061379283</v>
+        <v>0.09636397362326114</v>
       </c>
       <c r="C3">
-        <v>64.08620313912911</v>
+        <v>63.64606363036899</v>
       </c>
       <c r="D3">
-        <v>63.90220313912911</v>
+        <v>64.19106363036899</v>
       </c>
       <c r="E3">
-        <v>-37.671</v>
+        <v>-36.942</v>
       </c>
       <c r="F3">
-        <v>0.7290000000000001</v>
+        <v>1.458</v>
       </c>
       <c r="G3">
         <v>0.913</v>
@@ -1533,28 +1533,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M3">
-        <v>0.03666870000000001</v>
+        <v>0.07333740000000001</v>
       </c>
       <c r="N3">
-        <v>6.606664633333333</v>
+        <v>6.569995933333333</v>
       </c>
       <c r="O3">
-        <v>1.783799451</v>
+        <v>1.773898902</v>
       </c>
       <c r="P3">
-        <v>4.822865182333333</v>
+        <v>4.796097031333333</v>
       </c>
       <c r="Q3">
-        <v>8.062865182333333</v>
+        <v>8.036097031333332</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09719732385231598</v>
+        <v>0.09758121798291954</v>
       </c>
       <c r="T3">
-        <v>0.9413600363497479</v>
+        <v>0.9483911921698019</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>181.1717713835869</v>
+        <v>90.58588569179344</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09636397362326114</v>
+        <v>0.09613540663272946</v>
       </c>
       <c r="C4">
-        <v>63.64606363036899</v>
+        <v>63.20854748268144</v>
       </c>
       <c r="D4">
-        <v>64.19106363036899</v>
+        <v>64.48254748268144</v>
       </c>
       <c r="E4">
-        <v>-36.942</v>
+        <v>-36.213</v>
       </c>
       <c r="F4">
-        <v>1.458</v>
+        <v>2.187</v>
       </c>
       <c r="G4">
         <v>0.913</v>
@@ -1615,28 +1615,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M4">
-        <v>0.07333740000000001</v>
+        <v>0.1100061</v>
       </c>
       <c r="N4">
-        <v>6.569995933333333</v>
+        <v>6.533327233333333</v>
       </c>
       <c r="O4">
-        <v>1.773898902</v>
+        <v>1.763998353</v>
       </c>
       <c r="P4">
-        <v>4.796097031333333</v>
+        <v>4.769328880333333</v>
       </c>
       <c r="Q4">
-        <v>8.036097031333332</v>
+        <v>8.009328880333333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09758121798291954</v>
+        <v>0.09797302745642213</v>
       </c>
       <c r="T4">
-        <v>0.9483911921698019</v>
+        <v>0.9555673202748055</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>90.58588569179344</v>
+        <v>60.39059046119563</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09613540663272946</v>
+        <v>0.09590683964219779</v>
       </c>
       <c r="C5">
-        <v>63.20854748268144</v>
+        <v>62.77369059618005</v>
       </c>
       <c r="D5">
-        <v>64.48254748268144</v>
+        <v>64.77669059618005</v>
       </c>
       <c r="E5">
-        <v>-36.213</v>
+        <v>-35.48399999999999</v>
       </c>
       <c r="F5">
-        <v>2.187</v>
+        <v>2.916</v>
       </c>
       <c r="G5">
         <v>0.913</v>
@@ -1697,28 +1697,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M5">
-        <v>0.1100061</v>
+        <v>0.1466748</v>
       </c>
       <c r="N5">
-        <v>6.533327233333333</v>
+        <v>6.496658533333332</v>
       </c>
       <c r="O5">
-        <v>1.763998353</v>
+        <v>1.754097804</v>
       </c>
       <c r="P5">
-        <v>4.769328880333333</v>
+        <v>4.742560729333333</v>
       </c>
       <c r="Q5">
-        <v>8.009328880333333</v>
+        <v>7.982560729333333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09797302745642213</v>
+        <v>0.09837299962728936</v>
       </c>
       <c r="T5">
-        <v>0.9555673202748055</v>
+        <v>0.9628929510486635</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>60.39059046119563</v>
+        <v>45.29294284589671</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09590683964219779</v>
+        <v>0.09567827265166612</v>
       </c>
       <c r="C6">
-        <v>62.77369059618005</v>
+        <v>62.34152952902701</v>
       </c>
       <c r="D6">
-        <v>64.77669059618005</v>
+        <v>65.07352952902701</v>
       </c>
       <c r="E6">
-        <v>-35.48399999999999</v>
+        <v>-34.755</v>
       </c>
       <c r="F6">
-        <v>2.916</v>
+        <v>3.645</v>
       </c>
       <c r="G6">
         <v>0.913</v>
@@ -1779,28 +1779,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M6">
-        <v>0.1466748</v>
+        <v>0.1833435</v>
       </c>
       <c r="N6">
-        <v>6.496658533333332</v>
+        <v>6.459989833333332</v>
       </c>
       <c r="O6">
-        <v>1.754097804</v>
+        <v>1.744197255</v>
       </c>
       <c r="P6">
-        <v>4.742560729333333</v>
+        <v>4.715792578333333</v>
       </c>
       <c r="Q6">
-        <v>7.982560729333333</v>
+        <v>7.955792578333332</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09837299962728936</v>
+        <v>0.0987813922649117</v>
       </c>
       <c r="T6">
-        <v>0.9628929510486635</v>
+        <v>0.9703728056282868</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>45.29294284589671</v>
+        <v>36.23435427671738</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09567827265166612</v>
+        <v>0.09544970566113445</v>
       </c>
       <c r="C7">
-        <v>62.34152952902701</v>
+        <v>61.91210151257989</v>
       </c>
       <c r="D7">
-        <v>65.07352952902701</v>
+        <v>65.37310151257989</v>
       </c>
       <c r="E7">
-        <v>-34.755</v>
+        <v>-34.026</v>
       </c>
       <c r="F7">
-        <v>3.645</v>
+        <v>4.374000000000001</v>
       </c>
       <c r="G7">
         <v>0.913</v>
@@ -1861,28 +1861,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M7">
-        <v>0.1833435</v>
+        <v>0.2200122</v>
       </c>
       <c r="N7">
-        <v>6.459989833333332</v>
+        <v>6.423321133333332</v>
       </c>
       <c r="O7">
-        <v>1.744197255</v>
+        <v>1.734296706</v>
       </c>
       <c r="P7">
-        <v>4.715792578333333</v>
+        <v>4.689024427333333</v>
       </c>
       <c r="Q7">
-        <v>7.955792578333332</v>
+        <v>7.929024427333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0987813922649117</v>
+        <v>0.09919847410758983</v>
       </c>
       <c r="T7">
-        <v>0.9703728056282868</v>
+        <v>0.9780118060500298</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.23435427671738</v>
+        <v>30.19529523059781</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09544970566113445</v>
+        <v>0.09522113867060275</v>
       </c>
       <c r="C8">
-        <v>61.91210151257989</v>
+        <v>61.48544446695909</v>
       </c>
       <c r="D8">
-        <v>65.37310151257989</v>
+        <v>65.67544446695909</v>
       </c>
       <c r="E8">
-        <v>-34.026</v>
+        <v>-33.297</v>
       </c>
       <c r="F8">
-        <v>4.374000000000001</v>
+        <v>5.103</v>
       </c>
       <c r="G8">
         <v>0.913</v>
@@ -1943,28 +1943,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M8">
-        <v>0.2200122</v>
+        <v>0.2566809</v>
       </c>
       <c r="N8">
-        <v>6.423321133333332</v>
+        <v>6.386652433333333</v>
       </c>
       <c r="O8">
-        <v>1.734296706</v>
+        <v>1.724396157</v>
       </c>
       <c r="P8">
-        <v>4.689024427333333</v>
+        <v>4.662256276333332</v>
       </c>
       <c r="Q8">
-        <v>7.929024427333333</v>
+        <v>7.902256276333333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09919847410758983</v>
+        <v>0.09962452545226103</v>
       </c>
       <c r="T8">
-        <v>0.9780118060500298</v>
+        <v>0.985815086050735</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.19529523059781</v>
+        <v>25.8816816262267</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09522113867060274</v>
+        <v>0.09499257168007108</v>
       </c>
       <c r="C9">
-        <v>61.4854444669591</v>
+        <v>61.06159701704876</v>
       </c>
       <c r="D9">
-        <v>65.67544446695911</v>
+        <v>65.98059701704877</v>
       </c>
       <c r="E9">
-        <v>-33.297</v>
+        <v>-32.568</v>
       </c>
       <c r="F9">
-        <v>5.103000000000001</v>
+        <v>5.832000000000001</v>
       </c>
       <c r="G9">
         <v>0.913</v>
@@ -2025,28 +2025,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M9">
-        <v>0.2566809</v>
+        <v>0.2933496</v>
       </c>
       <c r="N9">
-        <v>6.386652433333333</v>
+        <v>6.349983733333333</v>
       </c>
       <c r="O9">
-        <v>1.724396157</v>
+        <v>1.714495608</v>
       </c>
       <c r="P9">
-        <v>4.662256276333332</v>
+        <v>4.635488125333333</v>
       </c>
       <c r="Q9">
-        <v>7.902256276333333</v>
+        <v>7.875488125333332</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09962452545226103</v>
+        <v>0.100059838782686</v>
       </c>
       <c r="T9">
-        <v>0.985815086050735</v>
+        <v>0.9937880025731947</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.88168162622669</v>
+        <v>22.64647142294836</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09499257168007108</v>
+        <v>0.09476400468953941</v>
       </c>
       <c r="C10">
-        <v>61.06159701704876</v>
+        <v>60.64059850894657</v>
       </c>
       <c r="D10">
-        <v>65.98059701704877</v>
+        <v>66.28859850894658</v>
       </c>
       <c r="E10">
-        <v>-32.568</v>
+        <v>-31.839</v>
       </c>
       <c r="F10">
-        <v>5.832000000000001</v>
+        <v>6.561</v>
       </c>
       <c r="G10">
         <v>0.913</v>
@@ -2107,28 +2107,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M10">
-        <v>0.2933496</v>
+        <v>0.3300183</v>
       </c>
       <c r="N10">
-        <v>6.349983733333333</v>
+        <v>6.313315033333333</v>
       </c>
       <c r="O10">
-        <v>1.714495608</v>
+        <v>1.704595059</v>
       </c>
       <c r="P10">
-        <v>4.635488125333333</v>
+        <v>4.608719974333333</v>
       </c>
       <c r="Q10">
-        <v>7.875488125333332</v>
+        <v>7.848719974333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.100059838782686</v>
+        <v>0.1005047194390543</v>
       </c>
       <c r="T10">
-        <v>0.9937880025731947</v>
+        <v>1.001936148030214</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.64647142294836</v>
+        <v>20.13019682039855</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09476400468953941</v>
+        <v>0.09453543769900774</v>
       </c>
       <c r="C11">
-        <v>60.64059850894657</v>
+        <v>60.2224890268758</v>
       </c>
       <c r="D11">
-        <v>66.28859850894658</v>
+        <v>66.5994890268758</v>
       </c>
       <c r="E11">
-        <v>-31.839</v>
+        <v>-31.11</v>
       </c>
       <c r="F11">
-        <v>6.561</v>
+        <v>7.29</v>
       </c>
       <c r="G11">
         <v>0.913</v>
@@ -2189,28 +2189,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M11">
-        <v>0.3300183</v>
+        <v>0.366687</v>
       </c>
       <c r="N11">
-        <v>6.313315033333333</v>
+        <v>6.276646333333333</v>
       </c>
       <c r="O11">
-        <v>1.704595059</v>
+        <v>1.69469451</v>
       </c>
       <c r="P11">
-        <v>4.608719974333333</v>
+        <v>4.581951823333333</v>
       </c>
       <c r="Q11">
-        <v>7.848719974333333</v>
+        <v>7.821951823333332</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1005047194390543</v>
+        <v>0.1009594863322308</v>
       </c>
       <c r="T11">
-        <v>1.001936148030214</v>
+        <v>1.010265363386278</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.13019682039855</v>
+        <v>18.11717713835869</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09453543769900774</v>
+        <v>0.09430687070847606</v>
       </c>
       <c r="C12">
-        <v>60.2224890268758</v>
+        <v>59.8073094105758</v>
       </c>
       <c r="D12">
-        <v>66.5994890268758</v>
+        <v>66.91330941057581</v>
       </c>
       <c r="E12">
-        <v>-31.11</v>
+        <v>-30.381</v>
       </c>
       <c r="F12">
-        <v>7.290000000000001</v>
+        <v>8.019</v>
       </c>
       <c r="G12">
         <v>0.913</v>
@@ -2271,28 +2271,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M12">
-        <v>0.366687</v>
+        <v>0.4033557</v>
       </c>
       <c r="N12">
-        <v>6.276646333333333</v>
+        <v>6.239977633333333</v>
       </c>
       <c r="O12">
-        <v>1.69469451</v>
+        <v>1.684793961</v>
       </c>
       <c r="P12">
-        <v>4.581951823333333</v>
+        <v>4.555183672333333</v>
       </c>
       <c r="Q12">
-        <v>7.821951823333332</v>
+        <v>7.795183672333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1009594863322308</v>
+        <v>0.1014244727061529</v>
       </c>
       <c r="T12">
-        <v>1.010265363386278</v>
+        <v>1.01878175212113</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.11717713835869</v>
+        <v>16.47016103487154</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09430687070847606</v>
+        <v>0.09407830371794437</v>
       </c>
       <c r="C13">
-        <v>59.8073094105758</v>
+        <v>59.39510127318647</v>
       </c>
       <c r="D13">
-        <v>66.91330941057581</v>
+        <v>67.23010127318648</v>
       </c>
       <c r="E13">
-        <v>-30.381</v>
+        <v>-29.652</v>
       </c>
       <c r="F13">
-        <v>8.019</v>
+        <v>8.748000000000001</v>
       </c>
       <c r="G13">
         <v>0.913</v>
@@ -2353,28 +2353,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M13">
-        <v>0.4033557</v>
+        <v>0.4400244</v>
       </c>
       <c r="N13">
-        <v>6.239977633333333</v>
+        <v>6.203308933333332</v>
       </c>
       <c r="O13">
-        <v>1.684793961</v>
+        <v>1.674893412</v>
       </c>
       <c r="P13">
-        <v>4.555183672333333</v>
+        <v>4.528415521333333</v>
       </c>
       <c r="Q13">
-        <v>7.795183672333334</v>
+        <v>7.768415521333333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1014244727061529</v>
+        <v>0.1019000269522095</v>
       </c>
       <c r="T13">
-        <v>1.01878175212113</v>
+        <v>1.02749169514541</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.47016103487154</v>
+        <v>15.09764761529891</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09407830371794437</v>
+        <v>0.0938497367274127</v>
       </c>
       <c r="C14">
-        <v>59.39510127318647</v>
+        <v>58.98590701964304</v>
       </c>
       <c r="D14">
-        <v>67.23010127318648</v>
+        <v>67.54990701964304</v>
       </c>
       <c r="E14">
-        <v>-29.652</v>
+        <v>-28.923</v>
       </c>
       <c r="F14">
-        <v>8.748000000000001</v>
+        <v>9.477</v>
       </c>
       <c r="G14">
         <v>0.913</v>
@@ -2435,28 +2435,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M14">
-        <v>0.4400244</v>
+        <v>0.4766931</v>
       </c>
       <c r="N14">
-        <v>6.203308933333332</v>
+        <v>6.166640233333332</v>
       </c>
       <c r="O14">
-        <v>1.674893412</v>
+        <v>1.664992863</v>
       </c>
       <c r="P14">
-        <v>4.528415521333333</v>
+        <v>4.501647370333332</v>
       </c>
       <c r="Q14">
-        <v>7.768415521333333</v>
+        <v>7.741647370333332</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1019000269522095</v>
+        <v>0.1023865134797847</v>
       </c>
       <c r="T14">
-        <v>1.02749169514541</v>
+        <v>1.036401866744962</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.09764761529891</v>
+        <v>13.93629010642976</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0938497367274127</v>
+        <v>0.09362116973688103</v>
       </c>
       <c r="C15">
-        <v>58.98590701964304</v>
+        <v>58.57976986559861</v>
       </c>
       <c r="D15">
-        <v>67.54990701964304</v>
+        <v>67.87276986559861</v>
       </c>
       <c r="E15">
-        <v>-28.923</v>
+        <v>-28.194</v>
       </c>
       <c r="F15">
-        <v>9.477</v>
+        <v>10.206</v>
       </c>
       <c r="G15">
         <v>0.913</v>
@@ -2517,28 +2517,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M15">
-        <v>0.4766931</v>
+        <v>0.5133618000000001</v>
       </c>
       <c r="N15">
-        <v>6.166640233333332</v>
+        <v>6.129971533333332</v>
       </c>
       <c r="O15">
-        <v>1.664992863</v>
+        <v>1.655092314</v>
       </c>
       <c r="P15">
-        <v>4.501647370333332</v>
+        <v>4.474879219333332</v>
       </c>
       <c r="Q15">
-        <v>7.741647370333332</v>
+        <v>7.714879219333332</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1023865134797847</v>
+        <v>0.1028843136475361</v>
       </c>
       <c r="T15">
-        <v>1.036401866744962</v>
+        <v>1.045519251637526</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>13.93629010642976</v>
+        <v>12.94084081311335</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09362116973688103</v>
+        <v>0.09355685274634935</v>
       </c>
       <c r="C16">
-        <v>58.57976986559861</v>
+        <v>57.94217815667655</v>
       </c>
       <c r="D16">
-        <v>67.87276986559861</v>
+        <v>67.96417815667655</v>
       </c>
       <c r="E16">
-        <v>-28.194</v>
+        <v>-27.465</v>
       </c>
       <c r="F16">
-        <v>10.206</v>
+        <v>10.935</v>
       </c>
       <c r="G16">
         <v>0.913</v>
@@ -2599,45 +2599,45 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M16">
-        <v>0.5133618000000001</v>
+        <v>0.5664330000000001</v>
       </c>
       <c r="N16">
-        <v>6.129971533333332</v>
+        <v>6.076900333333333</v>
       </c>
       <c r="O16">
-        <v>1.655092314</v>
+        <v>1.64076309</v>
       </c>
       <c r="P16">
-        <v>4.474879219333332</v>
+        <v>4.436137243333333</v>
       </c>
       <c r="Q16">
-        <v>7.714879219333332</v>
+        <v>7.676137243333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1028843136475361</v>
+        <v>0.103393826760411</v>
       </c>
       <c r="T16">
-        <v>1.045519251637526</v>
+        <v>1.054851163233445</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.27</v>
       </c>
       <c r="W16">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>12.94084081311335</v>
+        <v>11.72836563783066</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09355685274634935</v>
+        <v>0.09333923575581768</v>
       </c>
       <c r="C17">
-        <v>57.94217815667655</v>
+        <v>57.52429295857162</v>
       </c>
       <c r="D17">
-        <v>67.96417815667655</v>
+        <v>68.27529295857163</v>
       </c>
       <c r="E17">
-        <v>-27.465</v>
+        <v>-26.736</v>
       </c>
       <c r="F17">
-        <v>10.935</v>
+        <v>11.664</v>
       </c>
       <c r="G17">
         <v>0.913</v>
@@ -2681,28 +2681,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M17">
-        <v>0.566433</v>
+        <v>0.6041952</v>
       </c>
       <c r="N17">
-        <v>6.076900333333333</v>
+        <v>6.039138133333332</v>
       </c>
       <c r="O17">
-        <v>1.64076309</v>
+        <v>1.630567296</v>
       </c>
       <c r="P17">
-        <v>4.436137243333333</v>
+        <v>4.408570837333333</v>
       </c>
       <c r="Q17">
-        <v>7.676137243333333</v>
+        <v>7.648570837333333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.103393826760411</v>
+        <v>0.1039154711378782</v>
       </c>
       <c r="T17">
-        <v>1.054851163233445</v>
+        <v>1.064405263200695</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.72836563783066</v>
+        <v>10.99534278546624</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09333923575581768</v>
+        <v>0.09312161876528599</v>
       </c>
       <c r="C18">
-        <v>57.52429295857162</v>
+        <v>57.1092691954161</v>
       </c>
       <c r="D18">
-        <v>68.27529295857163</v>
+        <v>68.58926919541611</v>
       </c>
       <c r="E18">
-        <v>-26.736</v>
+        <v>-26.007</v>
       </c>
       <c r="F18">
-        <v>11.664</v>
+        <v>12.393</v>
       </c>
       <c r="G18">
         <v>0.913</v>
@@ -2763,28 +2763,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M18">
-        <v>0.6041952</v>
+        <v>0.6419574000000001</v>
       </c>
       <c r="N18">
-        <v>6.039138133333332</v>
+        <v>6.001375933333333</v>
       </c>
       <c r="O18">
-        <v>1.630567296</v>
+        <v>1.620371502</v>
       </c>
       <c r="P18">
-        <v>4.408570837333333</v>
+        <v>4.381004431333333</v>
       </c>
       <c r="Q18">
-        <v>7.648570837333333</v>
+        <v>7.621004431333333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1039154711378782</v>
+        <v>0.1044496852593807</v>
       </c>
       <c r="T18">
-        <v>1.064405263200695</v>
+        <v>1.074189582444264</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.99534278546624</v>
+        <v>10.34855791573293</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09312161876528599</v>
+        <v>0.09312738177475433</v>
       </c>
       <c r="C19">
-        <v>57.1092691954161</v>
+        <v>56.37191714649693</v>
       </c>
       <c r="D19">
-        <v>68.58926919541611</v>
+        <v>68.58091714649693</v>
       </c>
       <c r="E19">
-        <v>-26.007</v>
+        <v>-25.278</v>
       </c>
       <c r="F19">
-        <v>12.393</v>
+        <v>13.122</v>
       </c>
       <c r="G19">
         <v>0.913</v>
@@ -2845,45 +2845,45 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M19">
-        <v>0.6419574000000001</v>
+        <v>0.7020270000000002</v>
       </c>
       <c r="N19">
-        <v>6.001375933333333</v>
+        <v>5.941306333333332</v>
       </c>
       <c r="O19">
-        <v>1.620371502</v>
+        <v>1.60415271</v>
       </c>
       <c r="P19">
-        <v>4.381004431333333</v>
+        <v>4.337153623333332</v>
       </c>
       <c r="Q19">
-        <v>7.621004431333333</v>
+        <v>7.577153623333333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1044496852593807</v>
+        <v>0.1049969289936028</v>
       </c>
       <c r="T19">
-        <v>1.074189582444264</v>
+        <v>1.084212543620603</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.27</v>
       </c>
       <c r="W19">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.34855791573293</v>
+        <v>9.463073832392958</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09312738177475433</v>
+        <v>0.09292217478422264</v>
       </c>
       <c r="C20">
-        <v>56.37191714649693</v>
+        <v>55.94157236943556</v>
       </c>
       <c r="D20">
-        <v>68.58091714649693</v>
+        <v>68.87957236943556</v>
       </c>
       <c r="E20">
-        <v>-25.278</v>
+        <v>-24.549</v>
       </c>
       <c r="F20">
-        <v>13.122</v>
+        <v>13.851</v>
       </c>
       <c r="G20">
         <v>0.913</v>
@@ -2927,28 +2927,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M20">
-        <v>0.702027</v>
+        <v>0.7410285</v>
       </c>
       <c r="N20">
-        <v>5.941306333333332</v>
+        <v>5.902304833333333</v>
       </c>
       <c r="O20">
-        <v>1.60415271</v>
+        <v>1.593622305</v>
       </c>
       <c r="P20">
-        <v>4.337153623333332</v>
+        <v>4.308682528333333</v>
       </c>
       <c r="Q20">
-        <v>7.577153623333333</v>
+        <v>7.548682528333332</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1049969289936028</v>
+        <v>0.1055576849187934</v>
       </c>
       <c r="T20">
-        <v>1.084212543620603</v>
+        <v>1.094482985319815</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.463073832392961</v>
+        <v>8.965017314898596</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09292217478422264</v>
+        <v>0.09271696779369097</v>
       </c>
       <c r="C21">
-        <v>55.94157236943556</v>
+        <v>55.51384012862228</v>
       </c>
       <c r="D21">
-        <v>68.87957236943556</v>
+        <v>69.18084012862228</v>
       </c>
       <c r="E21">
-        <v>-24.549</v>
+        <v>-23.82</v>
       </c>
       <c r="F21">
-        <v>13.851</v>
+        <v>14.58</v>
       </c>
       <c r="G21">
         <v>0.913</v>
@@ -3009,28 +3009,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M21">
-        <v>0.7410285</v>
+        <v>0.7800300000000001</v>
       </c>
       <c r="N21">
-        <v>5.902304833333333</v>
+        <v>5.863303333333333</v>
       </c>
       <c r="O21">
-        <v>1.593622305</v>
+        <v>1.5830919</v>
       </c>
       <c r="P21">
-        <v>4.308682528333333</v>
+        <v>4.280211433333333</v>
       </c>
       <c r="Q21">
-        <v>7.548682528333332</v>
+        <v>7.520211433333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1055576849187934</v>
+        <v>0.1061324597421137</v>
       </c>
       <c r="T21">
-        <v>1.094482985319815</v>
+        <v>1.105010188061507</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.965017314898596</v>
+        <v>8.516766449153664</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09271696779369097</v>
+        <v>0.0925117608031593</v>
       </c>
       <c r="C22">
-        <v>55.51384012862228</v>
+        <v>55.08875485504566</v>
       </c>
       <c r="D22">
-        <v>69.18084012862228</v>
+        <v>69.48475485504567</v>
       </c>
       <c r="E22">
-        <v>-23.82</v>
+        <v>-23.09099999999999</v>
       </c>
       <c r="F22">
-        <v>14.58</v>
+        <v>15.309</v>
       </c>
       <c r="G22">
         <v>0.913</v>
@@ -3091,28 +3091,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M22">
-        <v>0.7800300000000001</v>
+        <v>0.8190315000000001</v>
       </c>
       <c r="N22">
-        <v>5.863303333333333</v>
+        <v>5.824301833333332</v>
       </c>
       <c r="O22">
-        <v>1.5830919</v>
+        <v>1.572561495</v>
       </c>
       <c r="P22">
-        <v>4.280211433333333</v>
+        <v>4.251740338333333</v>
       </c>
       <c r="Q22">
-        <v>7.520211433333333</v>
+        <v>7.491740338333333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1061324597421137</v>
+        <v>0.1067217858267839</v>
       </c>
       <c r="T22">
-        <v>1.105010188061507</v>
+        <v>1.115803902265014</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.516766449153664</v>
+        <v>8.111206142051106</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0925117608031593</v>
+        <v>0.09230655381262762</v>
       </c>
       <c r="C23">
-        <v>55.08875485504566</v>
+        <v>54.6663515873919</v>
       </c>
       <c r="D23">
-        <v>69.48475485504567</v>
+        <v>69.7913515873919</v>
       </c>
       <c r="E23">
-        <v>-23.091</v>
+        <v>-22.362</v>
       </c>
       <c r="F23">
-        <v>15.309</v>
+        <v>16.038</v>
       </c>
       <c r="G23">
         <v>0.913</v>
@@ -3173,28 +3173,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M23">
-        <v>0.8190315</v>
+        <v>0.858033</v>
       </c>
       <c r="N23">
-        <v>5.824301833333332</v>
+        <v>5.785300333333333</v>
       </c>
       <c r="O23">
-        <v>1.572561495</v>
+        <v>1.56203109</v>
       </c>
       <c r="P23">
-        <v>4.251740338333333</v>
+        <v>4.223269243333332</v>
       </c>
       <c r="Q23">
-        <v>7.491740338333333</v>
+        <v>7.463269243333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1067217858267839</v>
+        <v>0.1073262228367021</v>
       </c>
       <c r="T23">
-        <v>1.115803902265014</v>
+        <v>1.126874378371175</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.111206142051108</v>
+        <v>7.742514953776058</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09230655381262762</v>
+        <v>0.09223566682209594</v>
       </c>
       <c r="C24">
-        <v>54.6663515873919</v>
+        <v>54.04389251202472</v>
       </c>
       <c r="D24">
-        <v>69.7913515873919</v>
+        <v>69.89789251202473</v>
       </c>
       <c r="E24">
-        <v>-22.362</v>
+        <v>-21.633</v>
       </c>
       <c r="F24">
-        <v>16.038</v>
+        <v>16.767</v>
       </c>
       <c r="G24">
         <v>0.913</v>
@@ -3255,45 +3255,45 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M24">
-        <v>0.858033</v>
+        <v>0.9104481000000002</v>
       </c>
       <c r="N24">
-        <v>5.785300333333333</v>
+        <v>5.732885233333333</v>
       </c>
       <c r="O24">
-        <v>1.56203109</v>
+        <v>1.547879013</v>
       </c>
       <c r="P24">
-        <v>4.223269243333332</v>
+        <v>4.185006220333332</v>
       </c>
       <c r="Q24">
-        <v>7.463269243333333</v>
+        <v>7.425006220333332</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1073262228367021</v>
+        <v>0.1079463595092155</v>
       </c>
       <c r="T24">
-        <v>1.126874378371175</v>
+        <v>1.138232399311263</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.27</v>
       </c>
       <c r="W24">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.742514953776058</v>
+        <v>7.296773240927552</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09223566682209594</v>
+        <v>0.09203629983156426</v>
       </c>
       <c r="C25">
-        <v>54.04389251202472</v>
+        <v>53.61628627678088</v>
       </c>
       <c r="D25">
-        <v>69.89789251202473</v>
+        <v>70.19928627678088</v>
       </c>
       <c r="E25">
-        <v>-21.633</v>
+        <v>-20.904</v>
       </c>
       <c r="F25">
-        <v>16.767</v>
+        <v>17.496</v>
       </c>
       <c r="G25">
         <v>0.913</v>
@@ -3337,28 +3337,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M25">
-        <v>0.9104481000000002</v>
+        <v>0.9500328000000001</v>
       </c>
       <c r="N25">
-        <v>5.732885233333333</v>
+        <v>5.693300533333333</v>
       </c>
       <c r="O25">
-        <v>1.547879013</v>
+        <v>1.537191144</v>
       </c>
       <c r="P25">
-        <v>4.185006220333332</v>
+        <v>4.156109389333333</v>
       </c>
       <c r="Q25">
-        <v>7.425006220333332</v>
+        <v>7.396109389333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1079463595092155</v>
+        <v>0.1085828155678477</v>
       </c>
       <c r="T25">
-        <v>1.138232399311263</v>
+        <v>1.149889315539247</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.296773240927552</v>
+        <v>6.992741022555571</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09203629983156426</v>
+        <v>0.09183693284103259</v>
       </c>
       <c r="C26">
-        <v>53.61628627678088</v>
+        <v>53.19129046600001</v>
       </c>
       <c r="D26">
-        <v>70.19928627678088</v>
+        <v>70.50329046600001</v>
       </c>
       <c r="E26">
-        <v>-20.904</v>
+        <v>-20.175</v>
       </c>
       <c r="F26">
-        <v>17.496</v>
+        <v>18.225</v>
       </c>
       <c r="G26">
         <v>0.913</v>
@@ -3419,28 +3419,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M26">
-        <v>0.9500328000000001</v>
+        <v>0.9896175000000001</v>
       </c>
       <c r="N26">
-        <v>5.693300533333333</v>
+        <v>5.653715833333332</v>
       </c>
       <c r="O26">
-        <v>1.537191144</v>
+        <v>1.526503275</v>
       </c>
       <c r="P26">
-        <v>4.156109389333333</v>
+        <v>4.127212558333333</v>
       </c>
       <c r="Q26">
-        <v>7.396109389333333</v>
+        <v>7.367212558333332</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1085828155678477</v>
+        <v>0.1092362437880434</v>
       </c>
       <c r="T26">
-        <v>1.149889315539247</v>
+        <v>1.161857082866645</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.992741022555571</v>
+        <v>6.713031381653347</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09183693284103259</v>
+        <v>0.09163756585050091</v>
       </c>
       <c r="C27">
-        <v>53.19129046600001</v>
+        <v>52.76893914120738</v>
       </c>
       <c r="D27">
-        <v>70.50329046600001</v>
+        <v>70.80993914120738</v>
       </c>
       <c r="E27">
-        <v>-20.175</v>
+        <v>-19.446</v>
       </c>
       <c r="F27">
-        <v>18.225</v>
+        <v>18.954</v>
       </c>
       <c r="G27">
         <v>0.913</v>
@@ -3501,28 +3501,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M27">
-        <v>0.9896175000000001</v>
+        <v>1.0292022</v>
       </c>
       <c r="N27">
-        <v>5.653715833333332</v>
+        <v>5.614131133333332</v>
       </c>
       <c r="O27">
-        <v>1.526503275</v>
+        <v>1.515815406</v>
       </c>
       <c r="P27">
-        <v>4.127212558333333</v>
+        <v>4.098315727333333</v>
       </c>
       <c r="Q27">
-        <v>7.367212558333332</v>
+        <v>7.338315727333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1092362437880434</v>
+        <v>0.1099073322304066</v>
       </c>
       <c r="T27">
-        <v>1.161857082866645</v>
+        <v>1.174148303365052</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.713031381653347</v>
+        <v>6.454837866974373</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09163756585050091</v>
+        <v>0.09143819885996923</v>
       </c>
       <c r="C28">
-        <v>52.76893914120738</v>
+        <v>52.34926695910897</v>
       </c>
       <c r="D28">
-        <v>70.80993914120738</v>
+        <v>71.11926695910898</v>
       </c>
       <c r="E28">
-        <v>-19.446</v>
+        <v>-18.717</v>
       </c>
       <c r="F28">
-        <v>18.954</v>
+        <v>19.683</v>
       </c>
       <c r="G28">
         <v>0.913</v>
@@ -3583,28 +3583,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M28">
-        <v>1.0292022</v>
+        <v>1.0687869</v>
       </c>
       <c r="N28">
-        <v>5.614131133333332</v>
+        <v>5.574546433333333</v>
       </c>
       <c r="O28">
-        <v>1.515815406</v>
+        <v>1.505127537</v>
       </c>
       <c r="P28">
-        <v>4.098315727333333</v>
+        <v>4.069418896333333</v>
       </c>
       <c r="Q28">
-        <v>7.338315727333333</v>
+        <v>7.309418896333332</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1099073322304066</v>
+        <v>0.1105968066574921</v>
       </c>
       <c r="T28">
-        <v>1.174148303365052</v>
+        <v>1.18677626963054</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.454837866974373</v>
+        <v>6.215769797827174</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09143819885996923</v>
+        <v>0.09144323186943756</v>
       </c>
       <c r="C29">
-        <v>52.34926695910897</v>
+        <v>51.6124247461603</v>
       </c>
       <c r="D29">
-        <v>71.11926695910898</v>
+        <v>71.11142474616031</v>
       </c>
       <c r="E29">
-        <v>-18.717</v>
+        <v>-17.988</v>
       </c>
       <c r="F29">
-        <v>19.683</v>
+        <v>20.412</v>
       </c>
       <c r="G29">
         <v>0.913</v>
@@ -3665,45 +3665,45 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M29">
-        <v>1.0687869</v>
+        <v>1.1287836</v>
       </c>
       <c r="N29">
-        <v>5.574546433333333</v>
+        <v>5.514549733333332</v>
       </c>
       <c r="O29">
-        <v>1.505127537</v>
+        <v>1.488928428</v>
       </c>
       <c r="P29">
-        <v>4.069418896333333</v>
+        <v>4.025621305333333</v>
       </c>
       <c r="Q29">
-        <v>7.309418896333332</v>
+        <v>7.265621305333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1105968066574921</v>
+        <v>0.1113054331519966</v>
       </c>
       <c r="T29">
-        <v>1.18677626963054</v>
+        <v>1.199755012736736</v>
       </c>
       <c r="U29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.27</v>
       </c>
       <c r="W29">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.215769797827174</v>
+        <v>5.885391436705256</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09144323186943756</v>
+        <v>0.09125116487890587</v>
       </c>
       <c r="C30">
-        <v>51.6124247461603</v>
+        <v>51.18392655683567</v>
       </c>
       <c r="D30">
-        <v>71.11142474616031</v>
+        <v>71.41192655683568</v>
       </c>
       <c r="E30">
-        <v>-17.988</v>
+        <v>-17.25899999999999</v>
       </c>
       <c r="F30">
-        <v>20.412</v>
+        <v>21.14100000000001</v>
       </c>
       <c r="G30">
         <v>0.913</v>
@@ -3747,28 +3747,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M30">
-        <v>1.1287836</v>
+        <v>1.1690973</v>
       </c>
       <c r="N30">
-        <v>5.514549733333332</v>
+        <v>5.474236033333332</v>
       </c>
       <c r="O30">
-        <v>1.488928428</v>
+        <v>1.478043729</v>
       </c>
       <c r="P30">
-        <v>4.025621305333333</v>
+        <v>3.996192304333333</v>
       </c>
       <c r="Q30">
-        <v>7.265621305333333</v>
+        <v>7.236192304333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1113054331519966</v>
+        <v>0.1120340209562055</v>
       </c>
       <c r="T30">
-        <v>1.199755012736736</v>
+        <v>1.213099354240289</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.885391436705256</v>
+        <v>5.682446904405075</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09125116487890587</v>
+        <v>0.0910590978883742</v>
       </c>
       <c r="C31">
-        <v>51.18392655683567</v>
+        <v>50.75797885928475</v>
       </c>
       <c r="D31">
-        <v>71.41192655683568</v>
+        <v>71.71497885928476</v>
       </c>
       <c r="E31">
-        <v>-17.259</v>
+        <v>-16.53</v>
       </c>
       <c r="F31">
-        <v>21.141</v>
+        <v>21.87</v>
       </c>
       <c r="G31">
         <v>0.913</v>
@@ -3829,28 +3829,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M31">
-        <v>1.1690973</v>
+        <v>1.209411</v>
       </c>
       <c r="N31">
-        <v>5.474236033333332</v>
+        <v>5.433922333333332</v>
       </c>
       <c r="O31">
-        <v>1.478043729</v>
+        <v>1.46715903</v>
       </c>
       <c r="P31">
-        <v>3.996192304333333</v>
+        <v>3.966763303333332</v>
       </c>
       <c r="Q31">
-        <v>7.236192304333333</v>
+        <v>7.206763303333332</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1120340209562055</v>
+        <v>0.1127834255548203</v>
       </c>
       <c r="T31">
-        <v>1.213099354240289</v>
+        <v>1.226824962643944</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.682446904405075</v>
+        <v>5.493032007591573</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0910590978883742</v>
+        <v>0.09086703089784252</v>
       </c>
       <c r="C32">
-        <v>50.75797885928475</v>
+        <v>50.33461426261916</v>
       </c>
       <c r="D32">
-        <v>71.71497885928476</v>
+        <v>72.02061426261916</v>
       </c>
       <c r="E32">
-        <v>-16.53</v>
+        <v>-15.801</v>
       </c>
       <c r="F32">
-        <v>21.87</v>
+        <v>22.599</v>
       </c>
       <c r="G32">
         <v>0.913</v>
@@ -3911,28 +3911,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M32">
-        <v>1.209411</v>
+        <v>1.2497247</v>
       </c>
       <c r="N32">
-        <v>5.433922333333332</v>
+        <v>5.393608633333333</v>
       </c>
       <c r="O32">
-        <v>1.46715903</v>
+        <v>1.456274331</v>
       </c>
       <c r="P32">
-        <v>3.966763303333332</v>
+        <v>3.937334302333333</v>
       </c>
       <c r="Q32">
-        <v>7.206763303333332</v>
+        <v>7.177334302333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1127834255548203</v>
+        <v>0.1135545520258587</v>
       </c>
       <c r="T32">
-        <v>1.226824962643944</v>
+        <v>1.240948414769444</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.493032007591573</v>
+        <v>5.315837426701523</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09086703089784252</v>
+        <v>0.09067496390731085</v>
       </c>
       <c r="C33">
-        <v>50.33461426261916</v>
+        <v>49.91386593422462</v>
       </c>
       <c r="D33">
-        <v>72.02061426261916</v>
+        <v>72.32886593422462</v>
       </c>
       <c r="E33">
-        <v>-15.801</v>
+        <v>-15.072</v>
       </c>
       <c r="F33">
-        <v>22.599</v>
+        <v>23.328</v>
       </c>
       <c r="G33">
         <v>0.913</v>
@@ -3993,28 +3993,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M33">
-        <v>1.2497247</v>
+        <v>1.2900384</v>
       </c>
       <c r="N33">
-        <v>5.393608633333333</v>
+        <v>5.353294933333332</v>
       </c>
       <c r="O33">
-        <v>1.456274331</v>
+        <v>1.445389632</v>
       </c>
       <c r="P33">
-        <v>3.937334302333333</v>
+        <v>3.907905301333332</v>
       </c>
       <c r="Q33">
-        <v>7.177334302333333</v>
+        <v>7.147905301333332</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1135545520258587</v>
+        <v>0.1143483586872218</v>
       </c>
       <c r="T33">
-        <v>1.240948414769444</v>
+        <v>1.255487262545694</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.315837426701523</v>
+        <v>5.149717507117099</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09067496390731085</v>
+        <v>0.09048289691677917</v>
       </c>
       <c r="C34">
-        <v>49.91386593422462</v>
+        <v>49.49576761175975</v>
       </c>
       <c r="D34">
-        <v>72.32886593422462</v>
+        <v>72.63976761175975</v>
       </c>
       <c r="E34">
-        <v>-15.072</v>
+        <v>-14.343</v>
       </c>
       <c r="F34">
-        <v>23.328</v>
+        <v>24.057</v>
       </c>
       <c r="G34">
         <v>0.913</v>
@@ -4075,28 +4075,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M34">
-        <v>1.2900384</v>
+        <v>1.3303521</v>
       </c>
       <c r="N34">
-        <v>5.353294933333332</v>
+        <v>5.312981233333332</v>
       </c>
       <c r="O34">
-        <v>1.445389632</v>
+        <v>1.434504933</v>
       </c>
       <c r="P34">
-        <v>3.907905301333332</v>
+        <v>3.878476300333332</v>
       </c>
       <c r="Q34">
-        <v>7.147905301333332</v>
+        <v>7.118476300333333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1143483586872218</v>
+        <v>0.1151658610698197</v>
       </c>
       <c r="T34">
-        <v>1.255487262545694</v>
+        <v>1.270460105777952</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.149717507117099</v>
+        <v>4.993665461446884</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09048289691677917</v>
+        <v>0.09029082992624748</v>
       </c>
       <c r="C35">
-        <v>49.49576761175975</v>
+        <v>49.08035361546523</v>
       </c>
       <c r="D35">
-        <v>72.63976761175975</v>
+        <v>72.95335361546523</v>
       </c>
       <c r="E35">
-        <v>-14.343</v>
+        <v>-13.61399999999999</v>
       </c>
       <c r="F35">
-        <v>24.057</v>
+        <v>24.786</v>
       </c>
       <c r="G35">
         <v>0.913</v>
@@ -4157,28 +4157,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M35">
-        <v>1.3303521</v>
+        <v>1.3706658</v>
       </c>
       <c r="N35">
-        <v>5.312981233333332</v>
+        <v>5.272667533333332</v>
       </c>
       <c r="O35">
-        <v>1.434504933</v>
+        <v>1.423620234</v>
       </c>
       <c r="P35">
-        <v>3.878476300333332</v>
+        <v>3.849047299333332</v>
       </c>
       <c r="Q35">
-        <v>7.118476300333333</v>
+        <v>7.089047299333332</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1151658610698197</v>
+        <v>0.1160081362518902</v>
       </c>
       <c r="T35">
-        <v>1.270460105777952</v>
+        <v>1.285886671532399</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.993665461446884</v>
+        <v>4.846792947874917</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09029082992624748</v>
+        <v>0.09009876293571582</v>
       </c>
       <c r="C36">
-        <v>49.08035361546523</v>
+        <v>48.66765886079335</v>
       </c>
       <c r="D36">
-        <v>72.95335361546523</v>
+        <v>73.26965886079336</v>
       </c>
       <c r="E36">
-        <v>-13.61399999999999</v>
+        <v>-12.88499999999999</v>
       </c>
       <c r="F36">
-        <v>24.786</v>
+        <v>25.515</v>
       </c>
       <c r="G36">
         <v>0.913</v>
@@ -4239,28 +4239,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M36">
-        <v>1.3706658</v>
+        <v>1.4109795</v>
       </c>
       <c r="N36">
-        <v>5.272667533333332</v>
+        <v>5.232353833333333</v>
       </c>
       <c r="O36">
-        <v>1.423620234</v>
+        <v>1.412735535</v>
       </c>
       <c r="P36">
-        <v>3.849047299333332</v>
+        <v>3.819618298333333</v>
       </c>
       <c r="Q36">
-        <v>7.089047299333332</v>
+        <v>7.059618298333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1160081362518902</v>
+        <v>0.116876327593409</v>
       </c>
       <c r="T36">
-        <v>1.285886671532399</v>
+        <v>1.301787900848521</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.846792947874917</v>
+        <v>4.708313149364205</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09009876293571582</v>
+        <v>0.08990669594518415</v>
       </c>
       <c r="C37">
-        <v>48.66765886079335</v>
+        <v>48.25771887136781</v>
       </c>
       <c r="D37">
-        <v>73.26965886079336</v>
+        <v>73.58871887136782</v>
       </c>
       <c r="E37">
-        <v>-12.88499999999999</v>
+        <v>-12.15599999999999</v>
       </c>
       <c r="F37">
-        <v>25.515</v>
+        <v>26.24400000000001</v>
       </c>
       <c r="G37">
         <v>0.913</v>
@@ -4321,28 +4321,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M37">
-        <v>1.4109795</v>
+        <v>1.451293200000001</v>
       </c>
       <c r="N37">
-        <v>5.232353833333333</v>
+        <v>5.192040133333332</v>
       </c>
       <c r="O37">
-        <v>1.412735535</v>
+        <v>1.401850836</v>
       </c>
       <c r="P37">
-        <v>3.819618298333333</v>
+        <v>3.790189297333332</v>
       </c>
       <c r="Q37">
-        <v>7.059618298333333</v>
+        <v>7.030189297333332</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.116876327593409</v>
+        <v>0.1177716499143502</v>
       </c>
       <c r="T37">
-        <v>1.301787900848521</v>
+        <v>1.318186043580772</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.708313149364205</v>
+        <v>4.577526672992977</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08990669594518416</v>
+        <v>0.09038987895465248</v>
       </c>
       <c r="C38">
-        <v>48.2577188713678</v>
+        <v>46.73129982738818</v>
       </c>
       <c r="D38">
-        <v>73.5887188713678</v>
+        <v>72.79129982738819</v>
       </c>
       <c r="E38">
-        <v>-12.156</v>
+        <v>-11.427</v>
       </c>
       <c r="F38">
-        <v>26.244</v>
+        <v>26.973</v>
       </c>
       <c r="G38">
         <v>0.913</v>
@@ -4403,45 +4403,45 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M38">
-        <v>1.4512932</v>
+        <v>1.5590394</v>
       </c>
       <c r="N38">
-        <v>5.192040133333332</v>
+        <v>5.084293933333332</v>
       </c>
       <c r="O38">
-        <v>1.401850836</v>
+        <v>1.372759362</v>
       </c>
       <c r="P38">
-        <v>3.790189297333332</v>
+        <v>3.711534571333332</v>
       </c>
       <c r="Q38">
-        <v>7.030189297333332</v>
+        <v>6.951534571333331</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1177716499143502</v>
+        <v>0.118695395166115</v>
       </c>
       <c r="T38">
-        <v>1.318186043580772</v>
+        <v>1.335104762272777</v>
       </c>
       <c r="U38">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.27</v>
       </c>
       <c r="W38">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.577526672992978</v>
+        <v>4.261170906478266</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09038987895465248</v>
+        <v>0.0902160619641208</v>
       </c>
       <c r="C39">
-        <v>46.73129982738818</v>
+        <v>46.28715994585404</v>
       </c>
       <c r="D39">
-        <v>72.79129982738819</v>
+        <v>73.07615994585404</v>
       </c>
       <c r="E39">
-        <v>-11.427</v>
+        <v>-10.698</v>
       </c>
       <c r="F39">
-        <v>26.973</v>
+        <v>27.702</v>
       </c>
       <c r="G39">
         <v>0.913</v>
@@ -4485,28 +4485,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M39">
-        <v>1.5590394</v>
+        <v>1.6011756</v>
       </c>
       <c r="N39">
-        <v>5.084293933333332</v>
+        <v>5.042157733333332</v>
       </c>
       <c r="O39">
-        <v>1.372759362</v>
+        <v>1.361382588</v>
       </c>
       <c r="P39">
-        <v>3.711534571333332</v>
+        <v>3.680775145333333</v>
       </c>
       <c r="Q39">
-        <v>6.951534571333331</v>
+        <v>6.920775145333332</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.118695395166115</v>
+        <v>0.1196489386518077</v>
       </c>
       <c r="T39">
-        <v>1.335104762272777</v>
+        <v>1.35256924608388</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.261170906478266</v>
+        <v>4.149034829991995</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0902160619641208</v>
+        <v>0.09004224497358912</v>
       </c>
       <c r="C40">
-        <v>46.28715994585404</v>
+        <v>45.84525835618522</v>
       </c>
       <c r="D40">
-        <v>73.07615994585404</v>
+        <v>73.36325835618523</v>
       </c>
       <c r="E40">
-        <v>-10.698</v>
+        <v>-9.968999999999994</v>
       </c>
       <c r="F40">
-        <v>27.702</v>
+        <v>28.431</v>
       </c>
       <c r="G40">
         <v>0.913</v>
@@ -4567,28 +4567,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M40">
-        <v>1.6011756</v>
+        <v>1.6433118</v>
       </c>
       <c r="N40">
-        <v>5.042157733333332</v>
+        <v>5.000021533333332</v>
       </c>
       <c r="O40">
-        <v>1.361382588</v>
+        <v>1.350005814</v>
       </c>
       <c r="P40">
-        <v>3.680775145333333</v>
+        <v>3.650015719333333</v>
       </c>
       <c r="Q40">
-        <v>6.920775145333332</v>
+        <v>6.890015719333332</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1196489386518077</v>
+        <v>0.1206337458583428</v>
       </c>
       <c r="T40">
-        <v>1.35256924608388</v>
+        <v>1.370606335921575</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.149034829991995</v>
+        <v>4.042649321530662</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09004224497358912</v>
+        <v>0.09089042798305745</v>
       </c>
       <c r="C41">
-        <v>45.84525835618522</v>
+        <v>43.73624330553337</v>
       </c>
       <c r="D41">
-        <v>73.36325835618523</v>
+        <v>71.98324330553338</v>
       </c>
       <c r="E41">
-        <v>-9.968999999999994</v>
+        <v>-9.239999999999995</v>
       </c>
       <c r="F41">
-        <v>28.431</v>
+        <v>29.16</v>
       </c>
       <c r="G41">
         <v>0.913</v>
@@ -4649,45 +4649,45 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M41">
-        <v>1.6433118</v>
+        <v>1.787508</v>
       </c>
       <c r="N41">
-        <v>5.000021533333332</v>
+        <v>4.855825333333332</v>
       </c>
       <c r="O41">
-        <v>1.350005814</v>
+        <v>1.31107284</v>
       </c>
       <c r="P41">
-        <v>3.650015719333333</v>
+        <v>3.544752493333332</v>
       </c>
       <c r="Q41">
-        <v>6.890015719333332</v>
+        <v>6.784752493333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1206337458583428</v>
+        <v>0.1216513799717624</v>
       </c>
       <c r="T41">
-        <v>1.370606335921575</v>
+        <v>1.389244662087194</v>
       </c>
       <c r="U41">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V41">
         <v>0.27</v>
       </c>
       <c r="W41">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.042649321530662</v>
+        <v>3.716533483113547</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09089042798305745</v>
+        <v>0.09074216099252577</v>
       </c>
       <c r="C42">
-        <v>43.73624330553337</v>
+        <v>43.24472051219008</v>
       </c>
       <c r="D42">
-        <v>71.98324330553338</v>
+        <v>72.22072051219008</v>
       </c>
       <c r="E42">
-        <v>-9.239999999999995</v>
+        <v>-8.510999999999996</v>
       </c>
       <c r="F42">
-        <v>29.16</v>
+        <v>29.889</v>
       </c>
       <c r="G42">
         <v>0.913</v>
@@ -4731,28 +4731,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M42">
-        <v>1.787508</v>
+        <v>1.8321957</v>
       </c>
       <c r="N42">
-        <v>4.855825333333332</v>
+        <v>4.811137633333333</v>
       </c>
       <c r="O42">
-        <v>1.31107284</v>
+        <v>1.299007161</v>
       </c>
       <c r="P42">
-        <v>3.544752493333332</v>
+        <v>3.512130472333333</v>
       </c>
       <c r="Q42">
-        <v>6.784752493333333</v>
+        <v>6.752130472333333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1216513799717624</v>
+        <v>0.1227035101568233</v>
       </c>
       <c r="T42">
-        <v>1.389244662087194</v>
+        <v>1.408514795919444</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.716533483113547</v>
+        <v>3.625886324988827</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09074216099252577</v>
+        <v>0.09059389400199411</v>
       </c>
       <c r="C43">
-        <v>43.24472051219008</v>
+        <v>42.75476980948703</v>
       </c>
       <c r="D43">
-        <v>72.22072051219008</v>
+        <v>72.45976980948704</v>
       </c>
       <c r="E43">
-        <v>-8.510999999999996</v>
+        <v>-7.781999999999993</v>
       </c>
       <c r="F43">
-        <v>29.889</v>
+        <v>30.61800000000001</v>
       </c>
       <c r="G43">
         <v>0.913</v>
@@ -4813,28 +4813,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M43">
-        <v>1.8321957</v>
+        <v>1.8768834</v>
       </c>
       <c r="N43">
-        <v>4.811137633333333</v>
+        <v>4.766449933333332</v>
       </c>
       <c r="O43">
-        <v>1.299007161</v>
+        <v>1.286941482</v>
       </c>
       <c r="P43">
-        <v>3.512130472333333</v>
+        <v>3.479508451333333</v>
       </c>
       <c r="Q43">
-        <v>6.752130472333333</v>
+        <v>6.719508451333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1227035101568233</v>
+        <v>0.1237919206930933</v>
       </c>
       <c r="T43">
-        <v>1.408514795919444</v>
+        <v>1.42844941712522</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.625886324988827</v>
+        <v>3.539555698203379</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09059389400199408</v>
+        <v>0.09132454701146243</v>
       </c>
       <c r="C44">
-        <v>42.75476980948707</v>
+        <v>40.86281592301885</v>
       </c>
       <c r="D44">
-        <v>72.45976980948707</v>
+        <v>71.29681592301885</v>
       </c>
       <c r="E44">
-        <v>-7.781999999999996</v>
+        <v>-7.052999999999997</v>
       </c>
       <c r="F44">
-        <v>30.618</v>
+        <v>31.347</v>
       </c>
       <c r="G44">
         <v>0.913</v>
@@ -4895,45 +4895,45 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M44">
-        <v>1.8768834</v>
+        <v>2.0093427</v>
       </c>
       <c r="N44">
-        <v>4.766449933333332</v>
+        <v>4.633990633333332</v>
       </c>
       <c r="O44">
-        <v>1.286941482</v>
+        <v>1.251177471</v>
       </c>
       <c r="P44">
-        <v>3.479508451333333</v>
+        <v>3.382813162333332</v>
       </c>
       <c r="Q44">
-        <v>6.719508451333333</v>
+        <v>6.622813162333332</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1237919206930932</v>
+        <v>0.1249185210727411</v>
       </c>
       <c r="T44">
-        <v>1.42844941712522</v>
+        <v>1.449083498724181</v>
       </c>
       <c r="U44">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0.27</v>
       </c>
       <c r="W44">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.539555698203379</v>
+        <v>3.30622214584567</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09132454701146243</v>
+        <v>0.09119672002093074</v>
       </c>
       <c r="C45">
-        <v>40.86281592301885</v>
+        <v>40.33457177960342</v>
       </c>
       <c r="D45">
-        <v>71.29681592301885</v>
+        <v>71.49757177960342</v>
       </c>
       <c r="E45">
-        <v>-7.052999999999997</v>
+        <v>-6.323999999999998</v>
       </c>
       <c r="F45">
-        <v>31.347</v>
+        <v>32.076</v>
       </c>
       <c r="G45">
         <v>0.913</v>
@@ -4977,28 +4977,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M45">
-        <v>2.0093427</v>
+        <v>2.0560716</v>
       </c>
       <c r="N45">
-        <v>4.633990633333332</v>
+        <v>4.587261733333333</v>
       </c>
       <c r="O45">
-        <v>1.251177471</v>
+        <v>1.238560668</v>
       </c>
       <c r="P45">
-        <v>3.382813162333332</v>
+        <v>3.348701065333333</v>
       </c>
       <c r="Q45">
-        <v>6.622813162333332</v>
+        <v>6.588701065333332</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1249185210727411</v>
+        <v>0.1260853571802334</v>
       </c>
       <c r="T45">
-        <v>1.449083498724181</v>
+        <v>1.470454511808819</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.30622214584567</v>
+        <v>3.231080733440086</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09119672002093074</v>
+        <v>0.09106889303039907</v>
       </c>
       <c r="C46">
-        <v>40.33457177960342</v>
+        <v>39.80746139560907</v>
       </c>
       <c r="D46">
-        <v>71.49757177960342</v>
+        <v>71.69946139560908</v>
       </c>
       <c r="E46">
-        <v>-6.323999999999998</v>
+        <v>-5.594999999999992</v>
       </c>
       <c r="F46">
-        <v>32.076</v>
+        <v>32.80500000000001</v>
       </c>
       <c r="G46">
         <v>0.913</v>
@@ -5059,28 +5059,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M46">
-        <v>2.0560716</v>
+        <v>2.102800500000001</v>
       </c>
       <c r="N46">
-        <v>4.587261733333333</v>
+        <v>4.540532833333332</v>
       </c>
       <c r="O46">
-        <v>1.238560668</v>
+        <v>1.225943865</v>
       </c>
       <c r="P46">
-        <v>3.348701065333333</v>
+        <v>3.314588968333332</v>
       </c>
       <c r="Q46">
-        <v>6.588701065333332</v>
+        <v>6.554588968333332</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1260853571802334</v>
+        <v>0.1272946236916347</v>
       </c>
       <c r="T46">
-        <v>1.470454511808819</v>
+        <v>1.492602652641989</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.231080733440086</v>
+        <v>3.159278939363639</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09106889303039907</v>
+        <v>0.0909410660398674</v>
       </c>
       <c r="C47">
-        <v>39.80746139560907</v>
+        <v>39.28149440251343</v>
       </c>
       <c r="D47">
-        <v>71.69946139560908</v>
+        <v>71.90249440251344</v>
       </c>
       <c r="E47">
-        <v>-5.594999999999992</v>
+        <v>-4.865999999999993</v>
       </c>
       <c r="F47">
-        <v>32.80500000000001</v>
+        <v>33.53400000000001</v>
       </c>
       <c r="G47">
         <v>0.913</v>
@@ -5141,28 +5141,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M47">
-        <v>2.102800500000001</v>
+        <v>2.1495294</v>
       </c>
       <c r="N47">
-        <v>4.540532833333332</v>
+        <v>4.493803933333332</v>
       </c>
       <c r="O47">
-        <v>1.225943865</v>
+        <v>1.213327062</v>
       </c>
       <c r="P47">
-        <v>3.314588968333332</v>
+        <v>3.280476871333332</v>
       </c>
       <c r="Q47">
-        <v>6.554588968333332</v>
+        <v>6.520476871333332</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1272946236916347</v>
+        <v>0.1285486778516063</v>
       </c>
       <c r="T47">
-        <v>1.492602652641989</v>
+        <v>1.5155710949875</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.159278939363639</v>
+        <v>3.090598962420952</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0909410660398674</v>
+        <v>0.09081323904933572</v>
       </c>
       <c r="C48">
-        <v>39.28149440251343</v>
+        <v>38.75668054119856</v>
       </c>
       <c r="D48">
-        <v>71.90249440251344</v>
+        <v>72.10668054119857</v>
       </c>
       <c r="E48">
-        <v>-4.865999999999993</v>
+        <v>-4.136999999999993</v>
       </c>
       <c r="F48">
-        <v>33.53400000000001</v>
+        <v>34.26300000000001</v>
       </c>
       <c r="G48">
         <v>0.913</v>
@@ -5223,28 +5223,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M48">
-        <v>2.1495294</v>
+        <v>2.196258300000001</v>
       </c>
       <c r="N48">
-        <v>4.493803933333332</v>
+        <v>4.447075033333332</v>
       </c>
       <c r="O48">
-        <v>1.213327062</v>
+        <v>1.200710259</v>
       </c>
       <c r="P48">
-        <v>3.280476871333332</v>
+        <v>3.246364774333332</v>
       </c>
       <c r="Q48">
-        <v>6.520476871333332</v>
+        <v>6.486364774333332</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1285486778516063</v>
+        <v>0.1298500548100674</v>
       </c>
       <c r="T48">
-        <v>1.5155710949875</v>
+        <v>1.539406271006425</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.090598962420952</v>
+        <v>3.024841537688591</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09081323904933572</v>
+        <v>0.09341853205880404</v>
       </c>
       <c r="C49">
-        <v>38.75668054119856</v>
+        <v>34.08259818296955</v>
       </c>
       <c r="D49">
-        <v>72.10668054119857</v>
+        <v>68.16159818296956</v>
       </c>
       <c r="E49">
-        <v>-4.136999999999993</v>
+        <v>-3.407999999999994</v>
       </c>
       <c r="F49">
-        <v>34.26300000000001</v>
+        <v>34.992</v>
       </c>
       <c r="G49">
         <v>0.913</v>
@@ -5305,45 +5305,45 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M49">
-        <v>2.196258300000001</v>
+        <v>2.515924800000001</v>
       </c>
       <c r="N49">
-        <v>4.447075033333332</v>
+        <v>4.127408533333332</v>
       </c>
       <c r="O49">
-        <v>1.200710259</v>
+        <v>1.114400304</v>
       </c>
       <c r="P49">
-        <v>3.246364774333332</v>
+        <v>3.013008229333332</v>
       </c>
       <c r="Q49">
-        <v>6.486364774333332</v>
+        <v>6.253008229333332</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1298500548100674</v>
+        <v>0.1312014847284693</v>
       </c>
       <c r="T49">
-        <v>1.539406271006425</v>
+        <v>1.56415818456454</v>
       </c>
       <c r="U49">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V49">
         <v>0.27</v>
       </c>
       <c r="W49">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.024841537688591</v>
+        <v>2.640513473746644</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09341853205880404</v>
+        <v>0.09334764506827235</v>
       </c>
       <c r="C50">
-        <v>34.08259818296955</v>
+        <v>33.45521773864014</v>
       </c>
       <c r="D50">
-        <v>68.16159818296956</v>
+        <v>68.26321773864015</v>
       </c>
       <c r="E50">
-        <v>-3.407999999999994</v>
+        <v>-2.678999999999995</v>
       </c>
       <c r="F50">
-        <v>34.992</v>
+        <v>35.721</v>
       </c>
       <c r="G50">
         <v>0.913</v>
@@ -5387,28 +5387,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M50">
-        <v>2.515924800000001</v>
+        <v>2.568339900000001</v>
       </c>
       <c r="N50">
-        <v>4.127408533333332</v>
+        <v>4.074993433333332</v>
       </c>
       <c r="O50">
-        <v>1.114400304</v>
+        <v>1.100248227</v>
       </c>
       <c r="P50">
-        <v>3.013008229333332</v>
+        <v>2.974745206333332</v>
       </c>
       <c r="Q50">
-        <v>6.253008229333332</v>
+        <v>6.214745206333331</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1312014847284693</v>
+        <v>0.1326059118985732</v>
       </c>
       <c r="T50">
-        <v>1.56415818456454</v>
+        <v>1.589880761399444</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.640513473746644</v>
+        <v>2.586625443670182</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09334764506827235</v>
+        <v>0.09327675807774069</v>
       </c>
       <c r="C51">
-        <v>33.45521773864014</v>
+        <v>32.82814074824363</v>
       </c>
       <c r="D51">
-        <v>68.26321773864015</v>
+        <v>68.36514074824363</v>
       </c>
       <c r="E51">
-        <v>-2.678999999999995</v>
+        <v>-1.949999999999996</v>
       </c>
       <c r="F51">
-        <v>35.721</v>
+        <v>36.45</v>
       </c>
       <c r="G51">
         <v>0.913</v>
@@ -5469,28 +5469,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M51">
-        <v>2.568339900000001</v>
+        <v>2.620755</v>
       </c>
       <c r="N51">
-        <v>4.074993433333332</v>
+        <v>4.022578333333332</v>
       </c>
       <c r="O51">
-        <v>1.100248227</v>
+        <v>1.08609615</v>
       </c>
       <c r="P51">
-        <v>2.974745206333332</v>
+        <v>2.936482183333332</v>
       </c>
       <c r="Q51">
-        <v>6.214745206333331</v>
+        <v>6.176482183333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1326059118985732</v>
+        <v>0.1340665161554814</v>
       </c>
       <c r="T51">
-        <v>1.589880761399444</v>
+        <v>1.616632241307744</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.586625443670182</v>
+        <v>2.534892934796779</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09327675807774069</v>
+        <v>0.09465784108720901</v>
       </c>
       <c r="C52">
-        <v>32.82814074824363</v>
+        <v>30.16663754658194</v>
       </c>
       <c r="D52">
-        <v>68.36514074824363</v>
+        <v>66.43263754658194</v>
       </c>
       <c r="E52">
-        <v>-1.949999999999996</v>
+        <v>-1.220999999999997</v>
       </c>
       <c r="F52">
-        <v>36.45</v>
+        <v>37.179</v>
       </c>
       <c r="G52">
         <v>0.913</v>
@@ -5551,45 +5551,45 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M52">
-        <v>2.620755</v>
+        <v>2.818168200000001</v>
       </c>
       <c r="N52">
-        <v>4.022578333333332</v>
+        <v>3.825165133333332</v>
       </c>
       <c r="O52">
-        <v>1.08609615</v>
+        <v>1.032794586</v>
       </c>
       <c r="P52">
-        <v>2.936482183333332</v>
+        <v>2.792370547333332</v>
       </c>
       <c r="Q52">
-        <v>6.176482183333333</v>
+        <v>6.032370547333333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1340665161554814</v>
+        <v>0.1355867369126715</v>
       </c>
       <c r="T52">
-        <v>1.616632241307744</v>
+        <v>1.644475618355158</v>
       </c>
       <c r="U52">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V52">
         <v>0.27</v>
       </c>
       <c r="W52">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.534892934796779</v>
+        <v>2.357323219151125</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09465784108720901</v>
+        <v>0.09461542409667734</v>
       </c>
       <c r="C53">
-        <v>30.16663754658194</v>
+        <v>29.49536259168708</v>
       </c>
       <c r="D53">
-        <v>66.43263754658194</v>
+        <v>66.49036259168709</v>
       </c>
       <c r="E53">
-        <v>-1.220999999999997</v>
+        <v>-0.4919999999999973</v>
       </c>
       <c r="F53">
-        <v>37.179</v>
+        <v>37.908</v>
       </c>
       <c r="G53">
         <v>0.913</v>
@@ -5633,28 +5633,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M53">
-        <v>2.818168200000001</v>
+        <v>2.8734264</v>
       </c>
       <c r="N53">
-        <v>3.825165133333332</v>
+        <v>3.769906933333332</v>
       </c>
       <c r="O53">
-        <v>1.032794586</v>
+        <v>1.017874872</v>
       </c>
       <c r="P53">
-        <v>2.792370547333332</v>
+        <v>2.752032061333332</v>
       </c>
       <c r="Q53">
-        <v>6.032370547333333</v>
+        <v>5.992032061333332</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1355867369126715</v>
+        <v>0.1371703002014111</v>
       </c>
       <c r="T53">
-        <v>1.644475618355158</v>
+        <v>1.673479136112881</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.357323219151125</v>
+        <v>2.311990080321296</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09461542409667734</v>
+        <v>0.09457300710614566</v>
       </c>
       <c r="C54">
-        <v>29.49536259168708</v>
+        <v>28.8241880416201</v>
       </c>
       <c r="D54">
-        <v>66.49036259168709</v>
+        <v>66.54818804162011</v>
       </c>
       <c r="E54">
-        <v>-0.4919999999999973</v>
+        <v>0.237000000000009</v>
       </c>
       <c r="F54">
-        <v>37.908</v>
+        <v>38.63700000000001</v>
       </c>
       <c r="G54">
         <v>0.913</v>
@@ -5715,28 +5715,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M54">
-        <v>2.8734264</v>
+        <v>2.928684600000001</v>
       </c>
       <c r="N54">
-        <v>3.769906933333332</v>
+        <v>3.714648733333332</v>
       </c>
       <c r="O54">
-        <v>1.017874872</v>
+        <v>1.002955158</v>
       </c>
       <c r="P54">
-        <v>2.752032061333332</v>
+        <v>2.711693575333332</v>
       </c>
       <c r="Q54">
-        <v>5.992032061333332</v>
+        <v>5.951693575333332</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1371703002014111</v>
+        <v>0.1388212491620121</v>
       </c>
       <c r="T54">
-        <v>1.673479136112881</v>
+        <v>1.703716846115614</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.311990080321296</v>
+        <v>2.26836762597561</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09457300710614566</v>
+        <v>0.09453059011561399</v>
       </c>
       <c r="C55">
-        <v>28.8241880416201</v>
+        <v>28.15311415856973</v>
       </c>
       <c r="D55">
-        <v>66.54818804162011</v>
+        <v>66.60611415856974</v>
       </c>
       <c r="E55">
-        <v>0.237000000000009</v>
+        <v>0.9660000000000082</v>
       </c>
       <c r="F55">
-        <v>38.63700000000001</v>
+        <v>39.36600000000001</v>
       </c>
       <c r="G55">
         <v>0.913</v>
@@ -5797,28 +5797,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M55">
-        <v>2.928684600000001</v>
+        <v>2.983942800000001</v>
       </c>
       <c r="N55">
-        <v>3.714648733333332</v>
+        <v>3.659390533333332</v>
       </c>
       <c r="O55">
-        <v>1.002955158</v>
+        <v>0.9880354439999997</v>
       </c>
       <c r="P55">
-        <v>2.711693575333332</v>
+        <v>2.671355089333332</v>
       </c>
       <c r="Q55">
-        <v>5.951693575333332</v>
+        <v>5.911355089333332</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1388212491620121</v>
+        <v>0.1405439785122043</v>
       </c>
       <c r="T55">
-        <v>1.703716846115614</v>
+        <v>1.735269239161944</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.26836762597561</v>
+        <v>2.226360818087174</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09453059011561399</v>
+        <v>0.0944881731250823</v>
       </c>
       <c r="C56">
-        <v>28.15311415856973</v>
+        <v>27.48214120563839</v>
       </c>
       <c r="D56">
-        <v>66.60611415856974</v>
+        <v>66.6641412056384</v>
       </c>
       <c r="E56">
-        <v>0.9660000000000082</v>
+        <v>1.695000000000007</v>
       </c>
       <c r="F56">
-        <v>39.36600000000001</v>
+        <v>40.09500000000001</v>
       </c>
       <c r="G56">
         <v>0.913</v>
@@ -5879,28 +5879,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M56">
-        <v>2.983942800000001</v>
+        <v>3.039201000000001</v>
       </c>
       <c r="N56">
-        <v>3.659390533333332</v>
+        <v>3.604132333333332</v>
       </c>
       <c r="O56">
-        <v>0.9880354439999997</v>
+        <v>0.9731157299999997</v>
       </c>
       <c r="P56">
-        <v>2.671355089333332</v>
+        <v>2.631016603333332</v>
       </c>
       <c r="Q56">
-        <v>5.911355089333332</v>
+        <v>5.871016603333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1405439785122043</v>
+        <v>0.142343273611294</v>
       </c>
       <c r="T56">
-        <v>1.735269239161944</v>
+        <v>1.768223960788111</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.226360818087174</v>
+        <v>2.185881530485589</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0944881731250823</v>
+        <v>0.09444575613455063</v>
       </c>
       <c r="C57">
-        <v>27.48214120563839</v>
+        <v>26.81126944684613</v>
       </c>
       <c r="D57">
-        <v>66.6641412056384</v>
+        <v>66.72226944684614</v>
       </c>
       <c r="E57">
-        <v>1.695000000000007</v>
+        <v>2.424000000000007</v>
       </c>
       <c r="F57">
-        <v>40.09500000000001</v>
+        <v>40.82400000000001</v>
       </c>
       <c r="G57">
         <v>0.913</v>
@@ -5961,28 +5961,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M57">
-        <v>3.039201000000001</v>
+        <v>3.094459200000001</v>
       </c>
       <c r="N57">
-        <v>3.604132333333332</v>
+        <v>3.548874133333332</v>
       </c>
       <c r="O57">
-        <v>0.9731157299999997</v>
+        <v>0.9581960159999997</v>
       </c>
       <c r="P57">
-        <v>2.631016603333332</v>
+        <v>2.590678117333332</v>
       </c>
       <c r="Q57">
-        <v>5.871016603333333</v>
+        <v>5.830678117333332</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.142343273611294</v>
+        <v>0.1442243548512514</v>
       </c>
       <c r="T57">
-        <v>1.768223960788111</v>
+        <v>1.802676624306375</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.185881530485589</v>
+        <v>2.146847931726917</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09444575613455063</v>
+        <v>0.09440333914401895</v>
       </c>
       <c r="C58">
-        <v>26.81126944684613</v>
+        <v>26.14049914713467</v>
       </c>
       <c r="D58">
-        <v>66.72226944684614</v>
+        <v>66.78049914713468</v>
       </c>
       <c r="E58">
-        <v>2.424000000000007</v>
+        <v>3.153000000000006</v>
       </c>
       <c r="F58">
-        <v>40.82400000000001</v>
+        <v>41.553</v>
       </c>
       <c r="G58">
         <v>0.913</v>
@@ -6043,28 +6043,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M58">
-        <v>3.094459200000001</v>
+        <v>3.149717400000001</v>
       </c>
       <c r="N58">
-        <v>3.548874133333332</v>
+        <v>3.493615933333332</v>
       </c>
       <c r="O58">
-        <v>0.9581960159999997</v>
+        <v>0.9432763019999997</v>
       </c>
       <c r="P58">
-        <v>2.590678117333332</v>
+        <v>2.550339631333332</v>
       </c>
       <c r="Q58">
-        <v>5.830678117333332</v>
+        <v>5.790339631333332</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1442243548512514</v>
+        <v>0.1461929282419046</v>
       </c>
       <c r="T58">
-        <v>1.802676624306375</v>
+        <v>1.838731737290607</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.146847931726917</v>
+        <v>2.109183932924691</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09440333914401895</v>
+        <v>0.09436092215348728</v>
       </c>
       <c r="C59">
-        <v>26.14049914713467</v>
+        <v>25.46983057237144</v>
       </c>
       <c r="D59">
-        <v>66.78049914713468</v>
+        <v>66.83883057237145</v>
       </c>
       <c r="E59">
-        <v>3.153000000000006</v>
+        <v>3.882000000000012</v>
       </c>
       <c r="F59">
-        <v>41.553</v>
+        <v>42.28200000000001</v>
       </c>
       <c r="G59">
         <v>0.913</v>
@@ -6125,28 +6125,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M59">
-        <v>3.149717400000001</v>
+        <v>3.204975600000001</v>
       </c>
       <c r="N59">
-        <v>3.493615933333332</v>
+        <v>3.438357733333332</v>
       </c>
       <c r="O59">
-        <v>0.9432763019999997</v>
+        <v>0.9283565879999996</v>
       </c>
       <c r="P59">
-        <v>2.550339631333332</v>
+        <v>2.510001145333332</v>
       </c>
       <c r="Q59">
-        <v>5.790339631333332</v>
+        <v>5.750001145333332</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1461929282419046</v>
+        <v>0.1482552432225888</v>
       </c>
       <c r="T59">
-        <v>1.838731737290607</v>
+        <v>1.876503760416944</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.109183932924691</v>
+        <v>2.072818692701851</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09436092215348726</v>
+        <v>0.09431850516295559</v>
       </c>
       <c r="C60">
-        <v>25.46983057237146</v>
+        <v>24.79926398935358</v>
       </c>
       <c r="D60">
-        <v>66.83883057237146</v>
+        <v>66.89726398935359</v>
       </c>
       <c r="E60">
-        <v>3.882000000000005</v>
+        <v>4.611000000000004</v>
       </c>
       <c r="F60">
-        <v>42.282</v>
+        <v>43.011</v>
       </c>
       <c r="G60">
         <v>0.913</v>
@@ -6207,28 +6207,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M60">
-        <v>3.2049756</v>
+        <v>3.2602338</v>
       </c>
       <c r="N60">
-        <v>3.438357733333332</v>
+        <v>3.383099533333332</v>
       </c>
       <c r="O60">
-        <v>0.9283565879999998</v>
+        <v>0.9134368739999997</v>
       </c>
       <c r="P60">
-        <v>2.510001145333332</v>
+        <v>2.469662659333332</v>
       </c>
       <c r="Q60">
-        <v>5.750001145333332</v>
+        <v>5.709662659333333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1482552432225887</v>
+        <v>0.150418158934038</v>
       </c>
       <c r="T60">
-        <v>1.876503760416943</v>
+        <v>1.91611832125676</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.072818692701851</v>
+        <v>2.037686172486566</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09431850516295559</v>
+        <v>0.09427608817242392</v>
       </c>
       <c r="C61">
-        <v>24.79926398935358</v>
+        <v>24.12879966581202</v>
       </c>
       <c r="D61">
-        <v>66.89726398935359</v>
+        <v>66.95579966581202</v>
       </c>
       <c r="E61">
-        <v>4.611000000000004</v>
+        <v>5.340000000000003</v>
       </c>
       <c r="F61">
-        <v>43.011</v>
+        <v>43.74</v>
       </c>
       <c r="G61">
         <v>0.913</v>
@@ -6289,28 +6289,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M61">
-        <v>3.2602338</v>
+        <v>3.315492</v>
       </c>
       <c r="N61">
-        <v>3.383099533333332</v>
+        <v>3.327841333333332</v>
       </c>
       <c r="O61">
-        <v>0.9134368739999997</v>
+        <v>0.8985171599999998</v>
       </c>
       <c r="P61">
-        <v>2.469662659333332</v>
+        <v>2.429324173333332</v>
       </c>
       <c r="Q61">
-        <v>5.709662659333333</v>
+        <v>5.669324173333332</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.150418158934038</v>
+        <v>0.1526892204310598</v>
       </c>
       <c r="T61">
-        <v>1.91611832125676</v>
+        <v>1.957713610138568</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.037686172486566</v>
+        <v>2.003724736278456</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09427608817242392</v>
+        <v>0.1005569311818922</v>
       </c>
       <c r="C62">
-        <v>24.12879966581202</v>
+        <v>15.71969676016477</v>
       </c>
       <c r="D62">
-        <v>66.95579966581202</v>
+        <v>59.27569676016478</v>
       </c>
       <c r="E62">
-        <v>5.340000000000003</v>
+        <v>6.069000000000003</v>
       </c>
       <c r="F62">
-        <v>43.74</v>
+        <v>44.469</v>
       </c>
       <c r="G62">
         <v>0.913</v>
@@ -6371,45 +6371,45 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M62">
-        <v>3.315492</v>
+        <v>4.00221</v>
       </c>
       <c r="N62">
-        <v>3.327841333333332</v>
+        <v>2.641123333333333</v>
       </c>
       <c r="O62">
-        <v>0.8985171599999998</v>
+        <v>0.7131032999999999</v>
       </c>
       <c r="P62">
-        <v>2.429324173333332</v>
+        <v>1.928020033333333</v>
       </c>
       <c r="Q62">
-        <v>5.669324173333332</v>
+        <v>5.168020033333333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1526892204310598</v>
+        <v>0.1550767466202365</v>
       </c>
       <c r="T62">
-        <v>1.957713610138568</v>
+        <v>2.001441990757905</v>
       </c>
       <c r="U62">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V62">
         <v>0.27</v>
       </c>
       <c r="W62">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.003724736278456</v>
+        <v>1.65991622961647</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1005569311818922</v>
+        <v>0.1006181741913606</v>
       </c>
       <c r="C63">
-        <v>15.71969676016477</v>
+        <v>14.92447379467065</v>
       </c>
       <c r="D63">
-        <v>59.27569676016478</v>
+        <v>59.20947379467066</v>
       </c>
       <c r="E63">
-        <v>6.069000000000003</v>
+        <v>6.798000000000002</v>
       </c>
       <c r="F63">
-        <v>44.469</v>
+        <v>45.198</v>
       </c>
       <c r="G63">
         <v>0.913</v>
@@ -6453,28 +6453,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M63">
-        <v>4.00221</v>
+        <v>4.06782</v>
       </c>
       <c r="N63">
-        <v>2.641123333333333</v>
+        <v>2.575513333333332</v>
       </c>
       <c r="O63">
-        <v>0.7131032999999999</v>
+        <v>0.6953885999999998</v>
       </c>
       <c r="P63">
-        <v>1.928020033333333</v>
+        <v>1.880124733333333</v>
       </c>
       <c r="Q63">
-        <v>5.168020033333333</v>
+        <v>5.120124733333332</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1550767466202365</v>
+        <v>0.1575899320825278</v>
       </c>
       <c r="T63">
-        <v>2.001441990757905</v>
+        <v>2.047471865094049</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.65991622961647</v>
+        <v>1.633143387203301</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1006181741913606</v>
+        <v>0.1006794172008289</v>
       </c>
       <c r="C64">
-        <v>14.92447379467065</v>
+        <v>14.1293986329948</v>
       </c>
       <c r="D64">
-        <v>59.20947379467066</v>
+        <v>59.14339863299481</v>
       </c>
       <c r="E64">
-        <v>6.798000000000002</v>
+        <v>7.527000000000008</v>
       </c>
       <c r="F64">
-        <v>45.198</v>
+        <v>45.92700000000001</v>
       </c>
       <c r="G64">
         <v>0.913</v>
@@ -6535,28 +6535,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M64">
-        <v>4.06782</v>
+        <v>4.133430000000001</v>
       </c>
       <c r="N64">
-        <v>2.575513333333332</v>
+        <v>2.509903333333332</v>
       </c>
       <c r="O64">
-        <v>0.6953885999999998</v>
+        <v>0.6776738999999997</v>
       </c>
       <c r="P64">
-        <v>1.880124733333333</v>
+        <v>1.832229433333332</v>
       </c>
       <c r="Q64">
-        <v>5.120124733333332</v>
+        <v>5.072229433333332</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1575899320825278</v>
+        <v>0.1602389654076457</v>
       </c>
       <c r="T64">
-        <v>2.047471865094049</v>
+        <v>2.095989840745659</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.633143387203301</v>
+        <v>1.607220476295312</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1006794172008289</v>
+        <v>0.1007406602102972</v>
       </c>
       <c r="C65">
-        <v>14.1293986329948</v>
+        <v>13.33447078086116</v>
       </c>
       <c r="D65">
-        <v>59.14339863299481</v>
+        <v>59.07747078086117</v>
       </c>
       <c r="E65">
-        <v>7.527000000000008</v>
+        <v>8.256000000000007</v>
       </c>
       <c r="F65">
-        <v>45.92700000000001</v>
+        <v>46.65600000000001</v>
       </c>
       <c r="G65">
         <v>0.913</v>
@@ -6617,28 +6617,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M65">
-        <v>4.133430000000001</v>
+        <v>4.19904</v>
       </c>
       <c r="N65">
-        <v>2.509903333333332</v>
+        <v>2.444293333333333</v>
       </c>
       <c r="O65">
-        <v>0.6776738999999997</v>
+        <v>0.6599591999999999</v>
       </c>
       <c r="P65">
-        <v>1.832229433333332</v>
+        <v>1.784334133333333</v>
       </c>
       <c r="Q65">
-        <v>5.072229433333332</v>
+        <v>5.024334133333332</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1602389654076457</v>
+        <v>0.1630351672508256</v>
       </c>
       <c r="T65">
-        <v>2.095989840745659</v>
+        <v>2.147203259489027</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.607220476295312</v>
+        <v>1.582107656353198</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1007406602102972</v>
+        <v>0.1008019032197655</v>
       </c>
       <c r="C66">
-        <v>13.33447078086116</v>
+        <v>12.53968974619513</v>
       </c>
       <c r="D66">
-        <v>59.07747078086117</v>
+        <v>59.01168974619514</v>
       </c>
       <c r="E66">
-        <v>8.256000000000007</v>
+        <v>8.985000000000007</v>
       </c>
       <c r="F66">
-        <v>46.65600000000001</v>
+        <v>47.38500000000001</v>
       </c>
       <c r="G66">
         <v>0.913</v>
@@ -6699,28 +6699,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M66">
-        <v>4.19904</v>
+        <v>4.26465</v>
       </c>
       <c r="N66">
-        <v>2.444293333333333</v>
+        <v>2.378683333333332</v>
       </c>
       <c r="O66">
-        <v>0.6599591999999999</v>
+        <v>0.6422444999999998</v>
       </c>
       <c r="P66">
-        <v>1.784334133333333</v>
+        <v>1.736438833333332</v>
       </c>
       <c r="Q66">
-        <v>5.024334133333332</v>
+        <v>4.976438833333332</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1630351672508256</v>
+        <v>0.165991152056473</v>
       </c>
       <c r="T66">
-        <v>2.147203259489027</v>
+        <v>2.201343159303443</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.582107656353198</v>
+        <v>1.557767538563149</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1008019032197655</v>
+        <v>0.1008631462292339</v>
       </c>
       <c r="C67">
-        <v>12.53968974619513</v>
+        <v>11.74505503911134</v>
       </c>
       <c r="D67">
-        <v>59.01168974619514</v>
+        <v>58.94605503911135</v>
       </c>
       <c r="E67">
-        <v>8.985000000000007</v>
+        <v>9.714000000000006</v>
       </c>
       <c r="F67">
-        <v>47.38500000000001</v>
+        <v>48.114</v>
       </c>
       <c r="G67">
         <v>0.913</v>
@@ -6781,28 +6781,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M67">
-        <v>4.26465</v>
+        <v>4.33026</v>
       </c>
       <c r="N67">
-        <v>2.378683333333332</v>
+        <v>2.313073333333333</v>
       </c>
       <c r="O67">
-        <v>0.6422444999999998</v>
+        <v>0.6245297999999998</v>
       </c>
       <c r="P67">
-        <v>1.736438833333332</v>
+        <v>1.688543533333333</v>
       </c>
       <c r="Q67">
-        <v>4.976438833333332</v>
+        <v>4.928543533333333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.165991152056473</v>
+        <v>0.1691210183212761</v>
       </c>
       <c r="T67">
-        <v>2.201343159303443</v>
+        <v>2.258667759106943</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.557767538563149</v>
+        <v>1.534165000100071</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1008631462292339</v>
+        <v>0.1009243892387022</v>
       </c>
       <c r="C68">
-        <v>11.74505503911134</v>
+        <v>10.95056617190144</v>
       </c>
       <c r="D68">
-        <v>58.94605503911135</v>
+        <v>58.88056617190145</v>
       </c>
       <c r="E68">
-        <v>9.714000000000006</v>
+        <v>10.443</v>
       </c>
       <c r="F68">
-        <v>48.114</v>
+        <v>48.843</v>
       </c>
       <c r="G68">
         <v>0.913</v>
@@ -6863,28 +6863,28 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M68">
-        <v>4.33026</v>
+        <v>4.39587</v>
       </c>
       <c r="N68">
-        <v>2.313073333333333</v>
+        <v>2.247463333333332</v>
       </c>
       <c r="O68">
-        <v>0.6245297999999998</v>
+        <v>0.6068150999999997</v>
       </c>
       <c r="P68">
-        <v>1.688543533333333</v>
+        <v>1.640648233333333</v>
       </c>
       <c r="Q68">
-        <v>4.928543533333333</v>
+        <v>4.880648233333332</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1691210183212761</v>
+        <v>0.1724405734506127</v>
       </c>
       <c r="T68">
-        <v>2.258667759106943</v>
+        <v>2.319466577080352</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.534165000100071</v>
+        <v>1.51126701502395</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1009243892387022</v>
+        <v>0.1323445943793591</v>
       </c>
       <c r="C69">
-        <v>10.95056617190144</v>
+        <v>-11.15515274609032</v>
       </c>
       <c r="D69">
-        <v>58.88056617190145</v>
+        <v>37.50384725390969</v>
       </c>
       <c r="E69">
-        <v>10.443</v>
+        <v>11.17200000000001</v>
       </c>
       <c r="F69">
-        <v>48.843</v>
+        <v>49.57200000000001</v>
       </c>
       <c r="G69">
         <v>0.913</v>
@@ -6945,45 +6945,45 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M69">
-        <v>4.39587</v>
+        <v>7.277169600000002</v>
       </c>
       <c r="N69">
-        <v>2.247463333333332</v>
+        <v>-0.6338362666666697</v>
       </c>
       <c r="O69">
-        <v>0.6068150999999997</v>
+        <v>-0.1711357920000008</v>
       </c>
       <c r="P69">
-        <v>1.640648233333333</v>
+        <v>-0.4627004746666689</v>
       </c>
       <c r="Q69">
-        <v>4.880648233333332</v>
+        <v>2.777299525333331</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1724405734506127</v>
+        <v>0.1785172895342626</v>
       </c>
       <c r="T69">
-        <v>2.319466577080352</v>
+        <v>2.430763766206941</v>
       </c>
       <c r="U69">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.27</v>
+        <v>0.2464831931359686</v>
       </c>
       <c r="W69">
-        <v>0.06569999999999999</v>
+        <v>0.1106162672476398</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.51126701502395</v>
+        <v>0.9129007153184021</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1323445943793591</v>
+        <v>0.1333545943793591</v>
       </c>
       <c r="C70">
-        <v>-11.15515274609032</v>
+        <v>-12.31678436291131</v>
       </c>
       <c r="D70">
-        <v>37.50384725390969</v>
+        <v>37.0712156370887</v>
       </c>
       <c r="E70">
-        <v>11.17200000000001</v>
+        <v>11.90100000000001</v>
       </c>
       <c r="F70">
-        <v>49.57200000000001</v>
+        <v>50.30100000000001</v>
       </c>
       <c r="G70">
         <v>0.913</v>
@@ -7027,37 +7027,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M70">
-        <v>7.277169600000002</v>
+        <v>7.384186800000002</v>
       </c>
       <c r="N70">
-        <v>-0.6338362666666697</v>
+        <v>-0.7408534666666693</v>
       </c>
       <c r="O70">
-        <v>-0.1711357920000008</v>
+        <v>-0.2000304360000007</v>
       </c>
       <c r="P70">
-        <v>-0.4627004746666689</v>
+        <v>-0.5408230306666686</v>
       </c>
       <c r="Q70">
-        <v>2.777299525333331</v>
+        <v>2.699176969333331</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1785172895342626</v>
+        <v>0.1827984924224646</v>
       </c>
       <c r="T70">
-        <v>2.430763766206941</v>
+        <v>2.509175500600713</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2464831931359686</v>
+        <v>0.2429109729455922</v>
       </c>
       <c r="W70">
-        <v>0.1106162672476398</v>
+        <v>0.1111406691715871</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9129007153184021</v>
+        <v>0.8996702701688601</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1333545943793591</v>
+        <v>0.1343645943793591</v>
       </c>
       <c r="C71">
-        <v>-12.31678436291131</v>
+        <v>-13.46854842631436</v>
       </c>
       <c r="D71">
-        <v>37.0712156370887</v>
+        <v>36.64845157368566</v>
       </c>
       <c r="E71">
-        <v>11.90100000000001</v>
+        <v>12.63000000000001</v>
       </c>
       <c r="F71">
-        <v>50.30100000000001</v>
+        <v>51.03000000000001</v>
       </c>
       <c r="G71">
         <v>0.913</v>
@@ -7109,37 +7109,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M71">
-        <v>7.384186800000002</v>
+        <v>7.491204000000002</v>
       </c>
       <c r="N71">
-        <v>-0.7408534666666693</v>
+        <v>-0.8478706666666689</v>
       </c>
       <c r="O71">
-        <v>-0.2000304360000007</v>
+        <v>-0.2289250800000006</v>
       </c>
       <c r="P71">
-        <v>-0.5408230306666686</v>
+        <v>-0.6189455866666682</v>
       </c>
       <c r="Q71">
-        <v>2.699176969333331</v>
+        <v>2.621054413333332</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1827984924224646</v>
+        <v>0.1873651088365468</v>
       </c>
       <c r="T71">
-        <v>2.509175500600713</v>
+        <v>2.59281468395407</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2429109729455922</v>
+        <v>0.2394408161892267</v>
       </c>
       <c r="W71">
-        <v>0.1111406691715871</v>
+        <v>0.1116500881834215</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8996702701688601</v>
+        <v>0.8868178377378765</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1343645943793591</v>
+        <v>0.1353745943793591</v>
       </c>
       <c r="C72">
-        <v>-13.46854842631436</v>
+        <v>-14.61077872164407</v>
       </c>
       <c r="D72">
-        <v>36.64845157368566</v>
+        <v>36.23522127835594</v>
       </c>
       <c r="E72">
-        <v>12.63000000000001</v>
+        <v>13.35900000000001</v>
       </c>
       <c r="F72">
-        <v>51.03000000000001</v>
+        <v>51.75900000000001</v>
       </c>
       <c r="G72">
         <v>0.913</v>
@@ -7191,37 +7191,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M72">
-        <v>7.491204000000002</v>
+        <v>7.598221200000002</v>
       </c>
       <c r="N72">
-        <v>-0.8478706666666689</v>
+        <v>-0.9548878666666694</v>
       </c>
       <c r="O72">
-        <v>-0.2289250800000006</v>
+        <v>-0.2578197240000007</v>
       </c>
       <c r="P72">
-        <v>-0.6189455866666682</v>
+        <v>-0.6970681426666686</v>
       </c>
       <c r="Q72">
-        <v>2.621054413333332</v>
+        <v>2.542931857333331</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1873651088365468</v>
+        <v>0.1922466643136691</v>
       </c>
       <c r="T72">
-        <v>2.59281468395407</v>
+        <v>2.682222086849039</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2394408161892267</v>
+        <v>0.2360684103274066</v>
       </c>
       <c r="W72">
-        <v>0.1116500881834215</v>
+        <v>0.1121451573639367</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8868178377378765</v>
+        <v>0.8743274456570613</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1353745943793591</v>
+        <v>0.1363845943793591</v>
       </c>
       <c r="C73">
-        <v>-14.61077872164407</v>
+        <v>-15.7437941476874</v>
       </c>
       <c r="D73">
-        <v>36.23522127835594</v>
+        <v>35.8312058523126</v>
       </c>
       <c r="E73">
-        <v>13.359</v>
+        <v>14.088</v>
       </c>
       <c r="F73">
-        <v>51.759</v>
+        <v>52.488</v>
       </c>
       <c r="G73">
         <v>0.913</v>
@@ -7273,37 +7273,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M73">
-        <v>7.598221200000001</v>
+        <v>7.705238400000001</v>
       </c>
       <c r="N73">
-        <v>-0.9548878666666685</v>
+        <v>-1.061905066666668</v>
       </c>
       <c r="O73">
-        <v>-0.2578197240000005</v>
+        <v>-0.2867143680000004</v>
       </c>
       <c r="P73">
-        <v>-0.6970681426666679</v>
+        <v>-0.7751906986666677</v>
       </c>
       <c r="Q73">
-        <v>2.542931857333332</v>
+        <v>2.464809301333332</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.192246664313669</v>
+        <v>0.1974769023248715</v>
       </c>
       <c r="T73">
-        <v>2.682222086849038</v>
+        <v>2.778015732807932</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2360684103274066</v>
+        <v>0.2327896824061926</v>
       </c>
       <c r="W73">
-        <v>0.1121451573639367</v>
+        <v>0.1126264746227709</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8743274456570613</v>
+        <v>0.8621840089118245</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1363845943793591</v>
+        <v>0.1373945943793591</v>
       </c>
       <c r="C74">
-        <v>-15.7437941476874</v>
+        <v>-16.86789953743288</v>
       </c>
       <c r="D74">
-        <v>35.8312058523126</v>
+        <v>35.43610046256713</v>
       </c>
       <c r="E74">
-        <v>14.088</v>
+        <v>14.81700000000001</v>
       </c>
       <c r="F74">
-        <v>52.488</v>
+        <v>53.21700000000001</v>
       </c>
       <c r="G74">
         <v>0.913</v>
@@ -7355,37 +7355,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M74">
-        <v>7.705238400000001</v>
+        <v>7.812255600000001</v>
       </c>
       <c r="N74">
-        <v>-1.061905066666668</v>
+        <v>-1.168922266666669</v>
       </c>
       <c r="O74">
-        <v>-0.2867143680000004</v>
+        <v>-0.3156090120000005</v>
       </c>
       <c r="P74">
-        <v>-0.7751906986666677</v>
+        <v>-0.853313254666668</v>
       </c>
       <c r="Q74">
-        <v>2.464809301333332</v>
+        <v>2.386686745333332</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1974769023248715</v>
+        <v>0.2030945653739408</v>
       </c>
       <c r="T74">
-        <v>2.778015732807932</v>
+        <v>2.88090520439341</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2327896824061926</v>
+        <v>0.2296007826472037</v>
       </c>
       <c r="W74">
-        <v>0.1126264746227709</v>
+        <v>0.1130946051073905</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8621840089118245</v>
+        <v>0.8503732690637172</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1373945943793591</v>
+        <v>0.1384045943793591</v>
       </c>
       <c r="C75">
-        <v>-16.86789953743288</v>
+        <v>-17.98338642511985</v>
       </c>
       <c r="D75">
-        <v>35.43610046256713</v>
+        <v>35.04961357488015</v>
       </c>
       <c r="E75">
-        <v>14.81700000000001</v>
+        <v>15.54600000000001</v>
       </c>
       <c r="F75">
-        <v>53.21700000000001</v>
+        <v>53.94600000000001</v>
       </c>
       <c r="G75">
         <v>0.913</v>
@@ -7437,37 +7437,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M75">
-        <v>7.812255600000001</v>
+        <v>7.919272800000002</v>
       </c>
       <c r="N75">
-        <v>-1.168922266666669</v>
+        <v>-1.275939466666669</v>
       </c>
       <c r="O75">
-        <v>-0.3156090120000005</v>
+        <v>-0.3445036560000007</v>
       </c>
       <c r="P75">
-        <v>-0.853313254666668</v>
+        <v>-0.9314358106666684</v>
       </c>
       <c r="Q75">
-        <v>2.386686745333332</v>
+        <v>2.308564189333331</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2030945653739408</v>
+        <v>0.2091443563498616</v>
       </c>
       <c r="T75">
-        <v>2.88090520439341</v>
+        <v>2.991709250716234</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2296007826472037</v>
+        <v>0.2264980693681874</v>
       </c>
       <c r="W75">
-        <v>0.1130946051073905</v>
+        <v>0.1135500834167501</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8503732690637172</v>
+        <v>0.8388817384006939</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1384045943793591</v>
+        <v>0.1394145943793591</v>
       </c>
       <c r="C76">
-        <v>-17.98338642511985</v>
+        <v>-19.09053376363393</v>
       </c>
       <c r="D76">
-        <v>35.04961357488015</v>
+        <v>34.67146623636608</v>
       </c>
       <c r="E76">
-        <v>15.54600000000001</v>
+        <v>16.27500000000001</v>
       </c>
       <c r="F76">
-        <v>53.94600000000001</v>
+        <v>54.675</v>
       </c>
       <c r="G76">
         <v>0.913</v>
@@ -7519,37 +7519,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M76">
-        <v>7.919272800000002</v>
+        <v>8.026290000000001</v>
       </c>
       <c r="N76">
-        <v>-1.275939466666669</v>
+        <v>-1.382956666666669</v>
       </c>
       <c r="O76">
-        <v>-0.3445036560000007</v>
+        <v>-0.3733983000000006</v>
       </c>
       <c r="P76">
-        <v>-0.9314358106666684</v>
+        <v>-1.009558366666668</v>
       </c>
       <c r="Q76">
-        <v>2.308564189333331</v>
+        <v>2.230441633333331</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2091443563498616</v>
+        <v>0.2156781306038561</v>
       </c>
       <c r="T76">
-        <v>2.991709250716234</v>
+        <v>3.111377620744884</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2264980693681874</v>
+        <v>0.2234780951099449</v>
       </c>
       <c r="W76">
-        <v>0.1135500834167501</v>
+        <v>0.1139934156378601</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8388817384006939</v>
+        <v>0.8276966485553514</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1394145943793591</v>
+        <v>0.1404245943793591</v>
       </c>
       <c r="C77">
-        <v>-19.09053376363393</v>
+        <v>-20.18960859595857</v>
       </c>
       <c r="D77">
-        <v>34.67146623636608</v>
+        <v>34.30139140404143</v>
       </c>
       <c r="E77">
-        <v>16.27500000000001</v>
+        <v>17.004</v>
       </c>
       <c r="F77">
-        <v>54.675</v>
+        <v>55.404</v>
       </c>
       <c r="G77">
         <v>0.913</v>
@@ -7601,37 +7601,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M77">
-        <v>8.026290000000001</v>
+        <v>8.133307200000001</v>
       </c>
       <c r="N77">
-        <v>-1.382956666666669</v>
+        <v>-1.489973866666668</v>
       </c>
       <c r="O77">
-        <v>-0.3733983000000006</v>
+        <v>-0.4022929440000004</v>
       </c>
       <c r="P77">
-        <v>-1.009558366666668</v>
+        <v>-1.087680922666668</v>
       </c>
       <c r="Q77">
-        <v>2.230441633333331</v>
+        <v>2.152319077333332</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2156781306038561</v>
+        <v>0.2227563860456834</v>
       </c>
       <c r="T77">
-        <v>3.111377620744884</v>
+        <v>3.241018354942588</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2234780951099449</v>
+        <v>0.2205375938584983</v>
       </c>
       <c r="W77">
-        <v>0.1139934156378601</v>
+        <v>0.1144250812215725</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8276966485553514</v>
+        <v>0.8168059031796231</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1404245943793591</v>
+        <v>0.1414345943793591</v>
       </c>
       <c r="C78">
-        <v>-20.18960859595857</v>
+        <v>-21.28086668407943</v>
       </c>
       <c r="D78">
-        <v>34.30139140404143</v>
+        <v>33.93913331592057</v>
       </c>
       <c r="E78">
-        <v>17.004</v>
+        <v>17.733</v>
       </c>
       <c r="F78">
-        <v>55.404</v>
+        <v>56.133</v>
       </c>
       <c r="G78">
         <v>0.913</v>
@@ -7683,37 +7683,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M78">
-        <v>8.133307200000001</v>
+        <v>8.2403244</v>
       </c>
       <c r="N78">
-        <v>-1.489973866666668</v>
+        <v>-1.596991066666668</v>
       </c>
       <c r="O78">
-        <v>-0.4022929440000004</v>
+        <v>-0.4311875880000003</v>
       </c>
       <c r="P78">
-        <v>-1.087680922666668</v>
+        <v>-1.165803478666668</v>
       </c>
       <c r="Q78">
-        <v>2.152319077333332</v>
+        <v>2.074196521333332</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2227563860456834</v>
+        <v>0.2304501419607131</v>
       </c>
       <c r="T78">
-        <v>3.241018354942588</v>
+        <v>3.38193219646183</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2205375938584983</v>
+        <v>0.2176734692629334</v>
       </c>
       <c r="W78">
-        <v>0.1144250812215725</v>
+        <v>0.1148455347122014</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8168059031796231</v>
+        <v>0.8061980343071605</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1414345943793591</v>
+        <v>0.1868643207114381</v>
       </c>
       <c r="C79">
-        <v>-21.28086668407943</v>
+        <v>-32.93995538910518</v>
       </c>
       <c r="D79">
-        <v>33.93913331592057</v>
+        <v>23.00904461089483</v>
       </c>
       <c r="E79">
-        <v>17.733</v>
+        <v>18.46200000000001</v>
       </c>
       <c r="F79">
-        <v>56.133</v>
+        <v>56.86200000000001</v>
       </c>
       <c r="G79">
         <v>0.913</v>
@@ -7765,45 +7765,45 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M79">
-        <v>8.2403244</v>
+        <v>11.4178896</v>
       </c>
       <c r="N79">
-        <v>-1.596991066666668</v>
+        <v>-4.77455626666667</v>
       </c>
       <c r="O79">
-        <v>-0.4311875880000003</v>
+        <v>-1.289130192000001</v>
       </c>
       <c r="P79">
-        <v>-1.165803478666668</v>
+        <v>-3.485426074666669</v>
       </c>
       <c r="Q79">
-        <v>2.074196521333332</v>
+        <v>-0.245426074666669</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2304501419607131</v>
+        <v>0.2492966317411047</v>
       </c>
       <c r="T79">
-        <v>3.38193219646183</v>
+        <v>3.727112275403531</v>
       </c>
       <c r="U79">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.2176734692629334</v>
+        <v>0.157095580955696</v>
       </c>
       <c r="W79">
-        <v>0.1148455347122014</v>
+        <v>0.1692552073440962</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.8061980343071605</v>
+        <v>0.5818354850210963</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1868643207114381</v>
+        <v>0.1884143207114381</v>
       </c>
       <c r="C80">
-        <v>-32.93995538910518</v>
+        <v>-33.91902858630568</v>
       </c>
       <c r="D80">
-        <v>23.00904461089483</v>
+        <v>22.75897141369433</v>
       </c>
       <c r="E80">
-        <v>18.46200000000001</v>
+        <v>19.19100000000001</v>
       </c>
       <c r="F80">
-        <v>56.86200000000001</v>
+        <v>57.59100000000001</v>
       </c>
       <c r="G80">
         <v>0.913</v>
@@ -7847,37 +7847,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M80">
-        <v>11.4178896</v>
+        <v>11.5642728</v>
       </c>
       <c r="N80">
-        <v>-4.77455626666667</v>
+        <v>-4.920939466666669</v>
       </c>
       <c r="O80">
-        <v>-1.289130192000001</v>
+        <v>-1.328653656000001</v>
       </c>
       <c r="P80">
-        <v>-3.485426074666669</v>
+        <v>-3.592285810666668</v>
       </c>
       <c r="Q80">
-        <v>-0.245426074666669</v>
+        <v>-0.3522858106666682</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2492966317411047</v>
+        <v>0.2589869475383001</v>
       </c>
       <c r="T80">
-        <v>3.727112275403531</v>
+        <v>3.904593812327509</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.157095580955696</v>
+        <v>0.155107029298029</v>
       </c>
       <c r="W80">
-        <v>0.1692552073440962</v>
+        <v>0.1696545085169558</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5818354850210963</v>
+        <v>0.5744704788815889</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1884143207114381</v>
+        <v>0.1899643207114381</v>
       </c>
       <c r="C81">
-        <v>-33.91902858630568</v>
+        <v>-34.89272439950786</v>
       </c>
       <c r="D81">
-        <v>22.75897141369433</v>
+        <v>22.51427560049214</v>
       </c>
       <c r="E81">
-        <v>19.19100000000001</v>
+        <v>19.92000000000001</v>
       </c>
       <c r="F81">
-        <v>57.59100000000001</v>
+        <v>58.32000000000001</v>
       </c>
       <c r="G81">
         <v>0.913</v>
@@ -7929,37 +7929,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M81">
-        <v>11.5642728</v>
+        <v>11.710656</v>
       </c>
       <c r="N81">
-        <v>-4.920939466666669</v>
+        <v>-5.067322666666669</v>
       </c>
       <c r="O81">
-        <v>-1.328653656000001</v>
+        <v>-1.368177120000001</v>
       </c>
       <c r="P81">
-        <v>-3.592285810666668</v>
+        <v>-3.699145546666669</v>
       </c>
       <c r="Q81">
-        <v>-0.3522858106666682</v>
+        <v>-0.4591455466666687</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2589869475383001</v>
+        <v>0.2696462949152152</v>
       </c>
       <c r="T81">
-        <v>3.904593812327509</v>
+        <v>4.099823502943885</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.155107029298029</v>
+        <v>0.1531681914318036</v>
       </c>
       <c r="W81">
-        <v>0.1696545085169558</v>
+        <v>0.1700438271604938</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5744704788815889</v>
+        <v>0.567289597895569</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1899643207114381</v>
+        <v>0.1915143207114381</v>
       </c>
       <c r="C82">
-        <v>-34.89272439950786</v>
+        <v>-35.86121443048341</v>
       </c>
       <c r="D82">
-        <v>22.51427560049214</v>
+        <v>22.2747855695166</v>
       </c>
       <c r="E82">
-        <v>19.92000000000001</v>
+        <v>20.64900000000001</v>
       </c>
       <c r="F82">
-        <v>58.32000000000001</v>
+        <v>59.04900000000001</v>
       </c>
       <c r="G82">
         <v>0.913</v>
@@ -8011,37 +8011,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M82">
-        <v>11.710656</v>
+        <v>11.8570392</v>
       </c>
       <c r="N82">
-        <v>-5.067322666666669</v>
+        <v>-5.213705866666668</v>
       </c>
       <c r="O82">
-        <v>-1.368177120000001</v>
+        <v>-1.407700584000001</v>
       </c>
       <c r="P82">
-        <v>-3.699145546666669</v>
+        <v>-3.806005282666668</v>
       </c>
       <c r="Q82">
-        <v>-0.4591455466666687</v>
+        <v>-0.5660052826666679</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2696462949152152</v>
+        <v>0.2814276788581212</v>
       </c>
       <c r="T82">
-        <v>4.099823502943885</v>
+        <v>4.315603687309351</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1531681914318036</v>
+        <v>0.1512772261054851</v>
       </c>
       <c r="W82">
-        <v>0.1700438271604938</v>
+        <v>0.1704235329980186</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.567289597895569</v>
+        <v>0.5602860226129076</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1915143207114381</v>
+        <v>0.1930643207114381</v>
       </c>
       <c r="C83">
-        <v>-35.86121443048341</v>
+        <v>-36.82466305636886</v>
       </c>
       <c r="D83">
-        <v>22.2747855695166</v>
+        <v>22.04033694363115</v>
       </c>
       <c r="E83">
-        <v>20.64900000000001</v>
+        <v>21.37800000000001</v>
       </c>
       <c r="F83">
-        <v>59.04900000000001</v>
+        <v>59.77800000000001</v>
       </c>
       <c r="G83">
         <v>0.913</v>
@@ -8093,37 +8093,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M83">
-        <v>11.8570392</v>
+        <v>12.0034224</v>
       </c>
       <c r="N83">
-        <v>-5.213705866666668</v>
+        <v>-5.360089066666669</v>
       </c>
       <c r="O83">
-        <v>-1.407700584000001</v>
+        <v>-1.447224048000001</v>
       </c>
       <c r="P83">
-        <v>-3.806005282666668</v>
+        <v>-3.912865018666668</v>
       </c>
       <c r="Q83">
-        <v>-0.5660052826666679</v>
+        <v>-0.6728650186666685</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2814276788581212</v>
+        <v>0.2945181054613503</v>
       </c>
       <c r="T83">
-        <v>4.315603687309351</v>
+        <v>4.555359447715428</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1512772261054851</v>
+        <v>0.1494323818846865</v>
       </c>
       <c r="W83">
-        <v>0.1704235329980186</v>
+        <v>0.170793977717555</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5602860226129076</v>
+        <v>0.5534532662395795</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1930643207114381</v>
+        <v>0.1946143207114381</v>
       </c>
       <c r="C84">
-        <v>-36.82466305636886</v>
+        <v>-37.7832278059125</v>
       </c>
       <c r="D84">
-        <v>22.04033694363115</v>
+        <v>21.81077219408751</v>
       </c>
       <c r="E84">
-        <v>21.37800000000001</v>
+        <v>22.10700000000001</v>
       </c>
       <c r="F84">
-        <v>59.77800000000001</v>
+        <v>60.50700000000001</v>
       </c>
       <c r="G84">
         <v>0.913</v>
@@ -8175,37 +8175,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M84">
-        <v>12.0034224</v>
+        <v>12.1498056</v>
       </c>
       <c r="N84">
-        <v>-5.360089066666669</v>
+        <v>-5.50647226666667</v>
       </c>
       <c r="O84">
-        <v>-1.447224048000001</v>
+        <v>-1.486747512000001</v>
       </c>
       <c r="P84">
-        <v>-3.912865018666668</v>
+        <v>-4.019724754666669</v>
       </c>
       <c r="Q84">
-        <v>-0.6728650186666685</v>
+        <v>-0.779724754666669</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2945181054613503</v>
+        <v>0.3091485822531944</v>
       </c>
       <c r="T84">
-        <v>4.555359447715428</v>
+        <v>4.823321768169277</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1494323818846865</v>
+        <v>0.1476319917414975</v>
       </c>
       <c r="W84">
-        <v>0.170793977717555</v>
+        <v>0.1711554960583073</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5534532662395795</v>
+        <v>0.5467851545981387</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1946143207114381</v>
+        <v>0.1961643207114381</v>
       </c>
       <c r="C85">
-        <v>-37.7832278059125</v>
+        <v>-38.73705971245045</v>
       </c>
       <c r="D85">
-        <v>21.81077219408751</v>
+        <v>21.58594028754956</v>
       </c>
       <c r="E85">
-        <v>22.10700000000001</v>
+        <v>22.83600000000001</v>
       </c>
       <c r="F85">
-        <v>60.50700000000001</v>
+        <v>61.23600000000001</v>
       </c>
       <c r="G85">
         <v>0.913</v>
@@ -8257,37 +8257,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M85">
-        <v>12.1498056</v>
+        <v>12.2961888</v>
       </c>
       <c r="N85">
-        <v>-5.50647226666667</v>
+        <v>-5.65285546666667</v>
       </c>
       <c r="O85">
-        <v>-1.486747512000001</v>
+        <v>-1.526270976000001</v>
       </c>
       <c r="P85">
-        <v>-4.019724754666669</v>
+        <v>-4.126584490666669</v>
       </c>
       <c r="Q85">
-        <v>-0.779724754666669</v>
+        <v>-0.8865844906666696</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3091485822531944</v>
+        <v>0.3256078686440191</v>
       </c>
       <c r="T85">
-        <v>4.823321768169277</v>
+        <v>5.124779378679857</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1476319917414975</v>
+        <v>0.1458744680302891</v>
       </c>
       <c r="W85">
-        <v>0.1711554960583073</v>
+        <v>0.171508406819518</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5467851545981387</v>
+        <v>0.5402758075195895</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1961643207114381</v>
+        <v>0.1977143207114381</v>
       </c>
       <c r="C86">
-        <v>-38.73705971245045</v>
+        <v>-39.68630364527397</v>
       </c>
       <c r="D86">
-        <v>21.58594028754956</v>
+        <v>21.36569635472603</v>
       </c>
       <c r="E86">
-        <v>22.83600000000001</v>
+        <v>23.565</v>
       </c>
       <c r="F86">
-        <v>61.236</v>
+        <v>61.965</v>
       </c>
       <c r="G86">
         <v>0.913</v>
@@ -8339,37 +8339,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M86">
-        <v>12.2961888</v>
+        <v>12.442572</v>
       </c>
       <c r="N86">
-        <v>-5.652855466666669</v>
+        <v>-5.799238666666668</v>
       </c>
       <c r="O86">
-        <v>-1.526270976000001</v>
+        <v>-1.56579444</v>
       </c>
       <c r="P86">
-        <v>-4.126584490666668</v>
+        <v>-4.233444226666667</v>
       </c>
       <c r="Q86">
-        <v>-0.8865844906666678</v>
+        <v>-0.9934442266666674</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3256078686440189</v>
+        <v>0.3442617265536202</v>
       </c>
       <c r="T86">
-        <v>5.124779378679854</v>
+        <v>5.466431337258511</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1458744680302892</v>
+        <v>0.1441582978181681</v>
       </c>
       <c r="W86">
-        <v>0.171508406819518</v>
+        <v>0.1718530137981119</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5402758075195895</v>
+        <v>0.5339196215487708</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1977143207114381</v>
+        <v>0.1992643207114381</v>
       </c>
       <c r="C87">
-        <v>-39.68630364527397</v>
+        <v>-40.63109862091586</v>
       </c>
       <c r="D87">
-        <v>21.36569635472603</v>
+        <v>21.14990137908413</v>
       </c>
       <c r="E87">
-        <v>23.565</v>
+        <v>24.294</v>
       </c>
       <c r="F87">
-        <v>61.965</v>
+        <v>62.694</v>
       </c>
       <c r="G87">
         <v>0.913</v>
@@ -8421,37 +8421,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M87">
-        <v>12.442572</v>
+        <v>12.5889552</v>
       </c>
       <c r="N87">
-        <v>-5.799238666666668</v>
+        <v>-5.945621866666668</v>
       </c>
       <c r="O87">
-        <v>-1.56579444</v>
+        <v>-1.605317904000001</v>
       </c>
       <c r="P87">
-        <v>-4.233444226666667</v>
+        <v>-4.340303962666668</v>
       </c>
       <c r="Q87">
-        <v>-0.9934442266666674</v>
+        <v>-1.100303962666668</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3442617265536202</v>
+        <v>0.3655804213074502</v>
       </c>
       <c r="T87">
-        <v>5.466431337258511</v>
+        <v>5.856890718491262</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1441582978181681</v>
+        <v>0.1424820385412127</v>
       </c>
       <c r="W87">
-        <v>0.1718530137981119</v>
+        <v>0.1721896066609245</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5339196215487708</v>
+        <v>0.5277112538563432</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1992643207114381</v>
+        <v>0.2008143207114381</v>
       </c>
       <c r="C88">
-        <v>-40.63109862091586</v>
+        <v>-41.57157809576132</v>
       </c>
       <c r="D88">
-        <v>21.14990137908413</v>
+        <v>20.93842190423868</v>
       </c>
       <c r="E88">
-        <v>24.294</v>
+        <v>25.023</v>
       </c>
       <c r="F88">
-        <v>62.694</v>
+        <v>63.423</v>
       </c>
       <c r="G88">
         <v>0.913</v>
@@ -8503,37 +8503,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M88">
-        <v>12.5889552</v>
+        <v>12.7353384</v>
       </c>
       <c r="N88">
-        <v>-5.945621866666668</v>
+        <v>-6.092005066666669</v>
       </c>
       <c r="O88">
-        <v>-1.605317904000001</v>
+        <v>-1.644841368000001</v>
       </c>
       <c r="P88">
-        <v>-4.340303962666668</v>
+        <v>-4.447163698666668</v>
       </c>
       <c r="Q88">
-        <v>-1.100303962666668</v>
+        <v>-1.207163698666669</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3655804213074502</v>
+        <v>0.3901789152541771</v>
       </c>
       <c r="T88">
-        <v>5.856890718491262</v>
+        <v>6.30742077375982</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1424820385412127</v>
+        <v>0.1408443139602792</v>
       </c>
       <c r="W88">
-        <v>0.1721896066609245</v>
+        <v>0.1725184617567759</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5277112538563432</v>
+        <v>0.5216456072602933</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2008143207114381</v>
+        <v>0.2023643207114381</v>
       </c>
       <c r="C89">
-        <v>-41.57157809576132</v>
+        <v>-42.50787024127759</v>
       </c>
       <c r="D89">
-        <v>20.93842190423868</v>
+        <v>20.73112975872241</v>
       </c>
       <c r="E89">
-        <v>25.023</v>
+        <v>25.752</v>
       </c>
       <c r="F89">
-        <v>63.423</v>
+        <v>64.152</v>
       </c>
       <c r="G89">
         <v>0.913</v>
@@ -8585,37 +8585,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M89">
-        <v>12.7353384</v>
+        <v>12.8817216</v>
       </c>
       <c r="N89">
-        <v>-6.092005066666669</v>
+        <v>-6.238388266666668</v>
       </c>
       <c r="O89">
-        <v>-1.644841368000001</v>
+        <v>-1.684364832</v>
       </c>
       <c r="P89">
-        <v>-4.447163698666668</v>
+        <v>-4.554023434666668</v>
       </c>
       <c r="Q89">
-        <v>-1.207163698666669</v>
+        <v>-1.314023434666668</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3901789152541771</v>
+        <v>0.4188771581920253</v>
       </c>
       <c r="T89">
-        <v>6.30742077375982</v>
+        <v>6.83303917157314</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1408443139602792</v>
+        <v>0.1392438103925488</v>
       </c>
       <c r="W89">
-        <v>0.1725184617567759</v>
+        <v>0.1728398428731762</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5216456072602933</v>
+        <v>0.5157178162686991</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2023643207114381</v>
+        <v>0.2039143207114381</v>
       </c>
       <c r="C90">
-        <v>-42.50787024127759</v>
+        <v>-43.44009820305509</v>
       </c>
       <c r="D90">
-        <v>20.73112975872241</v>
+        <v>20.52790179694491</v>
       </c>
       <c r="E90">
-        <v>25.752</v>
+        <v>26.481</v>
       </c>
       <c r="F90">
-        <v>64.152</v>
+        <v>64.881</v>
       </c>
       <c r="G90">
         <v>0.913</v>
@@ -8667,37 +8667,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M90">
-        <v>12.8817216</v>
+        <v>13.0281048</v>
       </c>
       <c r="N90">
-        <v>-6.238388266666668</v>
+        <v>-6.384771466666669</v>
       </c>
       <c r="O90">
-        <v>-1.684364832</v>
+        <v>-1.723888296000001</v>
       </c>
       <c r="P90">
-        <v>-4.554023434666668</v>
+        <v>-4.660883170666668</v>
       </c>
       <c r="Q90">
-        <v>-1.314023434666668</v>
+        <v>-1.420883170666669</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4188771581920253</v>
+        <v>0.4527932634822094</v>
       </c>
       <c r="T90">
-        <v>6.83303917157314</v>
+        <v>7.454224550807061</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1392438103925488</v>
+        <v>0.1376792731971269</v>
       </c>
       <c r="W90">
-        <v>0.1728398428731762</v>
+        <v>0.1731540019420169</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5157178162686991</v>
+        <v>0.5099232340634328</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2039143207114381</v>
+        <v>0.2054643207114381</v>
       </c>
       <c r="C91">
-        <v>-43.44009820305509</v>
+        <v>-44.3683803447602</v>
       </c>
       <c r="D91">
-        <v>20.52790179694491</v>
+        <v>20.32861965523982</v>
       </c>
       <c r="E91">
-        <v>26.481</v>
+        <v>27.21000000000002</v>
       </c>
       <c r="F91">
-        <v>64.881</v>
+        <v>65.61000000000001</v>
       </c>
       <c r="G91">
         <v>0.913</v>
@@ -8749,37 +8749,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M91">
-        <v>13.0281048</v>
+        <v>13.174488</v>
       </c>
       <c r="N91">
-        <v>-6.384771466666669</v>
+        <v>-6.531154666666671</v>
       </c>
       <c r="O91">
-        <v>-1.723888296000001</v>
+        <v>-1.763411760000001</v>
       </c>
       <c r="P91">
-        <v>-4.660883170666668</v>
+        <v>-4.76774290666667</v>
       </c>
       <c r="Q91">
-        <v>-1.420883170666669</v>
+        <v>-1.52774290666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4527932634822094</v>
+        <v>0.4934925898304304</v>
       </c>
       <c r="T91">
-        <v>7.454224550807061</v>
+        <v>8.199647005887769</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1376792731971269</v>
+        <v>0.1361495034949365</v>
       </c>
       <c r="W91">
-        <v>0.1731540019420169</v>
+        <v>0.1734611796982168</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5099232340634328</v>
+        <v>0.5042574203516168</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2054643207114381</v>
+        <v>0.2397922880640456</v>
       </c>
       <c r="C92">
-        <v>-44.3683803447602</v>
+        <v>-48.69463773479757</v>
       </c>
       <c r="D92">
-        <v>20.32861965523982</v>
+        <v>16.73136226520244</v>
       </c>
       <c r="E92">
-        <v>27.21000000000002</v>
+        <v>27.93900000000001</v>
       </c>
       <c r="F92">
-        <v>65.61000000000001</v>
+        <v>66.33900000000001</v>
       </c>
       <c r="G92">
         <v>0.913</v>
@@ -8831,45 +8831,45 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M92">
-        <v>13.174488</v>
+        <v>15.6427362</v>
       </c>
       <c r="N92">
-        <v>-6.531154666666671</v>
+        <v>-8.999402866666671</v>
       </c>
       <c r="O92">
-        <v>-1.763411760000001</v>
+        <v>-2.429838774000001</v>
       </c>
       <c r="P92">
-        <v>-4.76774290666667</v>
+        <v>-6.56956409266667</v>
       </c>
       <c r="Q92">
-        <v>-1.52774290666667</v>
+        <v>-3.32956409266667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4934925898304304</v>
+        <v>0.5535469592850061</v>
       </c>
       <c r="T92">
-        <v>8.199647005887769</v>
+        <v>9.299563872671742</v>
       </c>
       <c r="U92">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1361495034949365</v>
+        <v>0.1146666399705698</v>
       </c>
       <c r="W92">
-        <v>0.1734611796982168</v>
+        <v>0.2087616062949396</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.5042574203516168</v>
+        <v>0.4246912591502586</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2397922880640456</v>
+        <v>0.2416922880640456</v>
       </c>
       <c r="C93">
-        <v>-48.69463773479757</v>
+        <v>-49.58591869347162</v>
       </c>
       <c r="D93">
-        <v>16.73136226520244</v>
+        <v>16.56908130652839</v>
       </c>
       <c r="E93">
-        <v>27.93900000000001</v>
+        <v>28.66800000000001</v>
       </c>
       <c r="F93">
-        <v>66.33900000000001</v>
+        <v>67.06800000000001</v>
       </c>
       <c r="G93">
         <v>0.913</v>
@@ -8913,37 +8913,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M93">
-        <v>15.6427362</v>
+        <v>15.8146344</v>
       </c>
       <c r="N93">
-        <v>-8.999402866666671</v>
+        <v>-9.17130106666667</v>
       </c>
       <c r="O93">
-        <v>-2.429838774000001</v>
+        <v>-2.476251288000001</v>
       </c>
       <c r="P93">
-        <v>-6.56956409266667</v>
+        <v>-6.695049778666669</v>
       </c>
       <c r="Q93">
-        <v>-3.32956409266667</v>
+        <v>-3.455049778666669</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5535469592850061</v>
+        <v>0.6170153291956321</v>
       </c>
       <c r="T93">
-        <v>9.299563872671742</v>
+        <v>10.46200935675571</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1146666399705698</v>
+        <v>0.1134202634491506</v>
       </c>
       <c r="W93">
-        <v>0.2087616062949396</v>
+        <v>0.2090555018786903</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4246912591502586</v>
+        <v>0.4200750498116689</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2416922880640456</v>
+        <v>0.2435922880640456</v>
       </c>
       <c r="C94">
-        <v>-49.58591869347162</v>
+        <v>-50.47408189842027</v>
       </c>
       <c r="D94">
-        <v>16.56908130652839</v>
+        <v>16.40991810157974</v>
       </c>
       <c r="E94">
-        <v>28.66800000000001</v>
+        <v>29.39700000000001</v>
       </c>
       <c r="F94">
-        <v>67.06800000000001</v>
+        <v>67.79700000000001</v>
       </c>
       <c r="G94">
         <v>0.913</v>
@@ -8995,37 +8995,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M94">
-        <v>15.8146344</v>
+        <v>15.9865326</v>
       </c>
       <c r="N94">
-        <v>-9.17130106666667</v>
+        <v>-9.343199266666671</v>
       </c>
       <c r="O94">
-        <v>-2.476251288000001</v>
+        <v>-2.522663802000001</v>
       </c>
       <c r="P94">
-        <v>-6.695049778666669</v>
+        <v>-6.82053546466667</v>
       </c>
       <c r="Q94">
-        <v>-3.455049778666669</v>
+        <v>-3.58053546466667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6170153291956321</v>
+        <v>0.6986175190807223</v>
       </c>
       <c r="T94">
-        <v>10.46200935675571</v>
+        <v>11.95658212200653</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1134202634491506</v>
+        <v>0.1122006907238909</v>
       </c>
       <c r="W94">
-        <v>0.2090555018786903</v>
+        <v>0.2093430771273065</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4200750498116689</v>
+        <v>0.4155581137921885</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2435922880640456</v>
+        <v>0.2454922880640456</v>
       </c>
       <c r="C95">
-        <v>-50.47408189842027</v>
+        <v>-51.35921634254564</v>
       </c>
       <c r="D95">
-        <v>16.40991810157974</v>
+        <v>16.25378365745437</v>
       </c>
       <c r="E95">
-        <v>29.39700000000001</v>
+        <v>30.12600000000001</v>
       </c>
       <c r="F95">
-        <v>67.79700000000001</v>
+        <v>68.52600000000001</v>
       </c>
       <c r="G95">
         <v>0.913</v>
@@ -9077,37 +9077,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M95">
-        <v>15.9865326</v>
+        <v>16.1584308</v>
       </c>
       <c r="N95">
-        <v>-9.343199266666671</v>
+        <v>-9.515097466666669</v>
       </c>
       <c r="O95">
-        <v>-2.522663802000001</v>
+        <v>-2.569076316000001</v>
       </c>
       <c r="P95">
-        <v>-6.82053546466667</v>
+        <v>-6.946021150666668</v>
       </c>
       <c r="Q95">
-        <v>-3.58053546466667</v>
+        <v>-3.706021150666669</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6986175190807223</v>
+        <v>0.8074204389275097</v>
       </c>
       <c r="T95">
-        <v>11.95658212200653</v>
+        <v>13.94934580900762</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1122006907238909</v>
+        <v>0.1110070663544878</v>
       </c>
       <c r="W95">
-        <v>0.2093430771273065</v>
+        <v>0.2096245337536118</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4155581137921885</v>
+        <v>0.4111372827943993</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2454922880640456</v>
+        <v>0.2473922880640457</v>
       </c>
       <c r="C96">
-        <v>-51.35921634254564</v>
+        <v>-52.24140766373027</v>
       </c>
       <c r="D96">
-        <v>16.25378365745437</v>
+        <v>16.10059233626974</v>
       </c>
       <c r="E96">
-        <v>30.12600000000001</v>
+        <v>30.85500000000001</v>
       </c>
       <c r="F96">
-        <v>68.52600000000001</v>
+        <v>69.25500000000001</v>
       </c>
       <c r="G96">
         <v>0.913</v>
@@ -9159,37 +9159,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M96">
-        <v>16.1584308</v>
+        <v>16.330329</v>
       </c>
       <c r="N96">
-        <v>-9.515097466666669</v>
+        <v>-9.68699566666667</v>
       </c>
       <c r="O96">
-        <v>-2.569076316000001</v>
+        <v>-2.615488830000001</v>
       </c>
       <c r="P96">
-        <v>-6.946021150666668</v>
+        <v>-7.071506836666669</v>
       </c>
       <c r="Q96">
-        <v>-3.706021150666669</v>
+        <v>-3.831506836666669</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8074204389275097</v>
+        <v>0.9597445267130121</v>
       </c>
       <c r="T96">
-        <v>13.94934580900762</v>
+        <v>16.73921497080916</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1110070663544878</v>
+        <v>0.1098385709191774</v>
       </c>
       <c r="W96">
-        <v>0.2096245337536118</v>
+        <v>0.209900064977258</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4111372827943993</v>
+        <v>0.4068095219228793</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2473922880640457</v>
+        <v>0.2492922880640456</v>
       </c>
       <c r="C97">
-        <v>-52.24140766373027</v>
+        <v>-53.12073830146571</v>
       </c>
       <c r="D97">
-        <v>16.10059233626974</v>
+        <v>15.9502616985343</v>
       </c>
       <c r="E97">
-        <v>30.85500000000001</v>
+        <v>31.58400000000001</v>
       </c>
       <c r="F97">
-        <v>69.25500000000001</v>
+        <v>69.98400000000001</v>
       </c>
       <c r="G97">
         <v>0.913</v>
@@ -9241,37 +9241,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M97">
-        <v>16.330329</v>
+        <v>16.5022272</v>
       </c>
       <c r="N97">
-        <v>-9.68699566666667</v>
+        <v>-9.858893866666671</v>
       </c>
       <c r="O97">
-        <v>-2.615488830000001</v>
+        <v>-2.661901344000001</v>
       </c>
       <c r="P97">
-        <v>-7.071506836666669</v>
+        <v>-7.19699252266667</v>
       </c>
       <c r="Q97">
-        <v>-3.831506836666669</v>
+        <v>-3.95699252266667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9597445267130121</v>
+        <v>1.188230658391266</v>
       </c>
       <c r="T97">
-        <v>16.73921497080916</v>
+        <v>20.92401871351145</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1098385709191774</v>
+        <v>0.1086944191387693</v>
       </c>
       <c r="W97">
-        <v>0.209900064977258</v>
+        <v>0.2101698559670782</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4068095219228793</v>
+        <v>0.4025719227361826</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2492922880640456</v>
+        <v>0.2511922880640456</v>
       </c>
       <c r="C98">
-        <v>-53.12073830146571</v>
+        <v>-53.99728764478753</v>
       </c>
       <c r="D98">
-        <v>15.9502616985343</v>
+        <v>15.80271235521248</v>
       </c>
       <c r="E98">
-        <v>31.58400000000001</v>
+        <v>32.31300000000001</v>
       </c>
       <c r="F98">
-        <v>69.98400000000001</v>
+        <v>70.71300000000001</v>
       </c>
       <c r="G98">
         <v>0.913</v>
@@ -9323,37 +9323,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M98">
-        <v>16.5022272</v>
+        <v>16.6741254</v>
       </c>
       <c r="N98">
-        <v>-9.858893866666671</v>
+        <v>-10.03079206666667</v>
       </c>
       <c r="O98">
-        <v>-2.661901344000001</v>
+        <v>-2.708313858000001</v>
       </c>
       <c r="P98">
-        <v>-7.19699252266667</v>
+        <v>-7.322478208666668</v>
       </c>
       <c r="Q98">
-        <v>-3.95699252266667</v>
+        <v>-4.082478208666668</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.188230658391263</v>
+        <v>1.569040877855017</v>
       </c>
       <c r="T98">
-        <v>20.9240187135114</v>
+        <v>27.8986916180152</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1086944191387693</v>
+        <v>0.1075738581167202</v>
       </c>
       <c r="W98">
-        <v>0.2101698559670782</v>
+        <v>0.2104340842560774</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4025719227361826</v>
+        <v>0.3984216967285932</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2511922880640456</v>
+        <v>0.2530922880640456</v>
       </c>
       <c r="C99">
-        <v>-53.99728764478753</v>
+        <v>-54.87113217207465</v>
       </c>
       <c r="D99">
-        <v>15.80271235521248</v>
+        <v>15.65786782792536</v>
       </c>
       <c r="E99">
-        <v>32.31300000000001</v>
+        <v>33.04200000000001</v>
       </c>
       <c r="F99">
-        <v>70.71300000000001</v>
+        <v>71.44200000000001</v>
       </c>
       <c r="G99">
         <v>0.913</v>
@@ -9405,37 +9405,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M99">
-        <v>16.6741254</v>
+        <v>16.8460236</v>
       </c>
       <c r="N99">
-        <v>-10.03079206666667</v>
+        <v>-10.20269026666667</v>
       </c>
       <c r="O99">
-        <v>-2.708313858000001</v>
+        <v>-2.754726372000001</v>
       </c>
       <c r="P99">
-        <v>-7.322478208666668</v>
+        <v>-7.447963894666669</v>
       </c>
       <c r="Q99">
-        <v>-4.082478208666668</v>
+        <v>-4.207963894666669</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.569040877855017</v>
+        <v>2.330661316782525</v>
       </c>
       <c r="T99">
-        <v>27.8986916180152</v>
+        <v>41.84803742702279</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1075738581167202</v>
+        <v>0.1064761656869577</v>
       </c>
       <c r="W99">
-        <v>0.2104340842560774</v>
+        <v>0.2106929201310154</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3984216967285932</v>
+        <v>0.3943561692109544</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2530922880640456</v>
+        <v>0.2549922880640456</v>
       </c>
       <c r="C100">
-        <v>-54.87113217207465</v>
+        <v>-55.74234558323037</v>
       </c>
       <c r="D100">
-        <v>15.65786782792536</v>
+        <v>15.51565441676964</v>
       </c>
       <c r="E100">
-        <v>33.04200000000001</v>
+        <v>33.77100000000001</v>
       </c>
       <c r="F100">
-        <v>71.44200000000001</v>
+        <v>72.17100000000001</v>
       </c>
       <c r="G100">
         <v>0.913</v>
@@ -9487,37 +9487,37 @@
         <v>6.643333333333333</v>
       </c>
       <c r="M100">
-        <v>16.8460236</v>
+        <v>17.0179218</v>
       </c>
       <c r="N100">
-        <v>-10.20269026666667</v>
+        <v>-10.37458846666667</v>
       </c>
       <c r="O100">
-        <v>-2.754726372000001</v>
+        <v>-2.801138886000001</v>
       </c>
       <c r="P100">
-        <v>-7.447963894666669</v>
+        <v>-7.57344958066667</v>
       </c>
       <c r="Q100">
-        <v>-4.207963894666669</v>
+        <v>-4.33344958066667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.330661316782525</v>
+        <v>4.615522633565051</v>
       </c>
       <c r="T100">
-        <v>41.84803742702279</v>
+        <v>83.69607485404559</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1064761656869577</v>
+        <v>0.1054006488618369</v>
       </c>
       <c r="W100">
-        <v>0.2106929201310154</v>
+        <v>0.2109465269983789</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3943561692109544</v>
+        <v>0.3903727735623589</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2549922880640456</v>
-      </c>
-      <c r="C101">
-        <v>-55.74234558323037</v>
-      </c>
-      <c r="D101">
-        <v>15.51565441676964</v>
-      </c>
-      <c r="E101">
-        <v>33.77100000000001</v>
-      </c>
-      <c r="F101">
-        <v>72.17100000000001</v>
-      </c>
-      <c r="G101">
-        <v>0.913</v>
-      </c>
-      <c r="H101">
-        <v>34.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.883333333333333</v>
-      </c>
-      <c r="K101">
-        <v>3.24</v>
-      </c>
-      <c r="L101">
-        <v>6.643333333333333</v>
-      </c>
-      <c r="M101">
-        <v>17.0179218</v>
-      </c>
-      <c r="N101">
-        <v>-10.37458846666667</v>
-      </c>
-      <c r="O101">
-        <v>-2.801138886000001</v>
-      </c>
-      <c r="P101">
-        <v>-7.57344958066667</v>
-      </c>
-      <c r="Q101">
-        <v>-4.33344958066667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.615522633565051</v>
-      </c>
-      <c r="T101">
-        <v>83.69607485404559</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1054006488618369</v>
-      </c>
-      <c r="W101">
-        <v>0.2109465269983789</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3903727735623589</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
